--- a/docs/manuscript/Table 1.xlsx
+++ b/docs/manuscript/Table 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\HPRU\Shingrix\HPRU_RZV\docs\tabs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\HPRU\Shingrix\HPRU_RZV\docs\manuscript\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2A0929-AA43-426C-A886-09BD62619E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49530C6C-32BA-43AF-95AC-BBBCB1E63E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12045" yWindow="3270" windowWidth="21900" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="70">
   <si>
     <t>[65,70)</t>
   </si>
@@ -234,16 +234,19 @@
     <t>Boost_2d</t>
   </si>
   <si>
-    <t>Additional eligibility A-1: Keeping 80+ eligible, single dose</t>
-  </si>
-  <si>
-    <t>Additional eligibility A-2: Keeping 80+ eligible, two doses</t>
-  </si>
-  <si>
     <t>Additional eligibility B-1: Those who reach age 80 years be called in on 80th birthday, keeping eligibility for higher ages to catch-up, single dose</t>
   </si>
   <si>
     <t>Additional eligibility B-2: Those who reach age 80 years be called in on 80th birthday, keeping eligibility for higher ages to catch-up, two doses</t>
+  </si>
+  <si>
+    <t>Existing programme</t>
+  </si>
+  <si>
+    <t>Extension to 80+, one dose</t>
+  </si>
+  <si>
+    <t>Extension to 80+, two doses</t>
   </si>
 </sst>
 </file>
@@ -285,7 +288,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -336,11 +339,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.24994659260841701"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="2" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="2" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.24994659260841701"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -373,28 +413,14 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -406,7 +432,46 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -688,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A42E2-CD23-4C67-BA97-748E6A031FBF}">
-  <dimension ref="A1:AI37"/>
+  <dimension ref="A1:AI38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
@@ -706,7 +771,7 @@
     <col min="13" max="13" width="8.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -723,26 +788,26 @@
       <c r="D1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="25"/>
-      <c r="G1" s="26" t="s">
+      <c r="F1" s="17"/>
+      <c r="G1" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26" t="s">
+      <c r="H1" s="18"/>
+      <c r="I1" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26" t="s">
+      <c r="J1" s="18"/>
+      <c r="K1" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="26"/>
-      <c r="M1" s="27" t="s">
+      <c r="L1" s="18"/>
+      <c r="M1" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="27"/>
+      <c r="N1" s="19"/>
       <c r="O1" s="8" t="s">
         <v>18</v>
       </c>
@@ -848,867 +913,790 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+    <row r="3" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="24"/>
+      <c r="S3"/>
+      <c r="T3"/>
+      <c r="U3"/>
+      <c r="V3"/>
+      <c r="W3"/>
+      <c r="X3"/>
+      <c r="Y3"/>
+      <c r="Z3"/>
+      <c r="AA3"/>
+      <c r="AB3"/>
+      <c r="AC3"/>
+      <c r="AD3"/>
+      <c r="AE3"/>
+      <c r="AF3"/>
+      <c r="AG3"/>
+      <c r="AH3"/>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A4" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="15" t="str">
-        <f>T3</f>
+      <c r="B4" s="14" t="str">
+        <f>T4</f>
         <v>[65,70)</v>
       </c>
-      <c r="C3" s="16">
-        <f>V3 / 1000</f>
+      <c r="C4" s="15">
+        <f>V4 / 1000</f>
         <v>2965.5050000000001</v>
       </c>
-      <c r="D3" s="17">
-        <f t="shared" ref="D3:E5" si="0">W3 / 1000</f>
+      <c r="D4" s="15">
+        <f t="shared" ref="D4:E6" si="0">W4 / 1000</f>
         <v>640.87300000000005</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E4" s="25">
         <f t="shared" si="0"/>
         <v>308.56384904957997</v>
       </c>
-      <c r="F3" s="19">
-        <f>AD3</f>
+      <c r="F4" s="26">
+        <f>AD4</f>
         <v>0.50216009675581297</v>
       </c>
-      <c r="G3" s="17">
-        <f>Y3 / 1000</f>
+      <c r="G4" s="15">
+        <f>Y4 / 1000</f>
         <v>617.12769809915994</v>
       </c>
-      <c r="H3" s="19">
-        <f>AE3</f>
+      <c r="H4" s="26">
+        <f>AE4</f>
         <v>0.50216009675581297</v>
       </c>
-      <c r="I3" s="17">
-        <f>-Z3</f>
+      <c r="I4" s="15">
+        <f>-Z4</f>
         <v>33706.0578608129</v>
       </c>
-      <c r="J3" s="19">
-        <f>AF3</f>
+      <c r="J4" s="26">
+        <f>AF4</f>
         <v>0.54679755127354501</v>
       </c>
-      <c r="K3" s="17">
-        <f>AB3</f>
+      <c r="K4" s="15">
+        <f>AB4</f>
         <v>3186.60962820637</v>
       </c>
-      <c r="L3" s="19">
-        <f>AG3</f>
+      <c r="L4" s="26">
+        <f>AG4</f>
         <v>0.51115069742946195</v>
       </c>
-      <c r="M3" s="20">
-        <f>-AA3/1000000</f>
+      <c r="M4" s="27">
+        <f>-AA4/1000000</f>
         <v>6.2360332324265695</v>
       </c>
-      <c r="N3" s="19">
-        <f>AH3</f>
+      <c r="N4" s="26">
+        <f>AH4</f>
         <v>0.47407751644561502</v>
       </c>
-      <c r="O3" s="20">
-        <f>AC3</f>
+      <c r="O4" s="27">
+        <f>AC4</f>
         <v>113.377224862967</v>
       </c>
-      <c r="P3" s="20">
-        <f>(K3 * 20 + M3 * 1000) /G3</f>
+      <c r="P4" s="27">
+        <f>(K4 * 20 + M4 * 1000) /G4</f>
         <v>113.37722486296749</v>
       </c>
-      <c r="Q3" s="18">
-        <f>E3/I3*1000</f>
+      <c r="Q4" s="25">
+        <f>E4/I4*1000</f>
         <v>9.1545516928670647</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S4" t="s">
         <v>49</v>
       </c>
-      <c r="T3" t="s">
+      <c r="T4" t="s">
         <v>0</v>
       </c>
-      <c r="U3" t="s">
+      <c r="U4" t="s">
         <v>59</v>
       </c>
-      <c r="V3">
+      <c r="V4">
         <v>2965505</v>
       </c>
-      <c r="W3">
+      <c r="W4">
         <v>640873</v>
       </c>
-      <c r="X3">
+      <c r="X4">
         <v>308563.84904957999</v>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <v>617127.69809915998</v>
       </c>
-      <c r="Z3">
+      <c r="Z4">
         <v>-33706.0578608129</v>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <v>-6236033.2324265698</v>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <v>3186.60962820637</v>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <v>113.377224862967</v>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <v>0.50216009675581297</v>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <v>0.50216009675581297</v>
       </c>
-      <c r="AF3">
+      <c r="AF4">
         <v>0.54679755127354501</v>
       </c>
-      <c r="AG3">
+      <c r="AG4">
         <v>0.51115069742946195</v>
       </c>
-      <c r="AH3">
+      <c r="AH4">
         <v>0.47407751644561502</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AI4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="15" t="str">
-        <f t="shared" ref="B4:B5" si="1">T4</f>
+      <c r="B5" s="14" t="str">
+        <f t="shared" ref="B5:B6" si="1">T5</f>
         <v>[70,75)</v>
       </c>
-      <c r="C4" s="16">
-        <f t="shared" ref="C4:C5" si="2">V4 / 1000</f>
+      <c r="C5" s="15">
+        <f t="shared" ref="C5:C6" si="2">V5 / 1000</f>
         <v>2662.3220000000001</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D5" s="15">
         <f t="shared" si="0"/>
         <v>1054.3696604547902</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E5" s="25">
         <f t="shared" si="0"/>
         <v>241.45137207275201</v>
       </c>
-      <c r="F4" s="19">
-        <f t="shared" ref="F4:F5" si="3">AD4</f>
+      <c r="F5" s="26">
+        <f t="shared" ref="F5:F6" si="3">AD5</f>
         <v>0.89510063316451904</v>
       </c>
-      <c r="G4" s="17">
-        <f t="shared" ref="G4:G5" si="4">Y4 / 1000</f>
+      <c r="G5" s="15">
+        <f t="shared" ref="G5:G6" si="4">Y5 / 1000</f>
         <v>482.90274414550504</v>
       </c>
-      <c r="H4" s="19">
-        <f t="shared" ref="H4:H5" si="5">AE4</f>
+      <c r="H5" s="26">
+        <f t="shared" ref="H5:H6" si="5">AE5</f>
         <v>0.89510063316451904</v>
       </c>
-      <c r="I4" s="17">
-        <f t="shared" ref="I4:I5" si="6">-Z4</f>
+      <c r="I5" s="15">
+        <f t="shared" ref="I5:I6" si="6">-Z5</f>
         <v>22908.903181728401</v>
       </c>
-      <c r="J4" s="19">
-        <f t="shared" ref="J4:J5" si="7">AF4</f>
+      <c r="J5" s="26">
+        <f t="shared" ref="J5:J6" si="7">AF5</f>
         <v>0.91843793158320297</v>
       </c>
-      <c r="K4" s="17">
-        <f t="shared" ref="K4:K5" si="8">AB4</f>
+      <c r="K5" s="15">
+        <f t="shared" ref="K5:K6" si="8">AB5</f>
         <v>2450.0437441876402</v>
       </c>
-      <c r="L4" s="19">
-        <f t="shared" ref="L4:L5" si="9">AG4</f>
+      <c r="L5" s="26">
+        <f t="shared" ref="L5:L6" si="9">AG5</f>
         <v>0.90415194787729403</v>
       </c>
-      <c r="M4" s="20">
-        <f t="shared" ref="M4:M5" si="10">-AA4/1000000</f>
+      <c r="M5" s="27">
+        <f t="shared" ref="M5:M6" si="10">-AA5/1000000</f>
         <v>5.3964384847435598</v>
       </c>
-      <c r="N4" s="19">
-        <f t="shared" ref="N4:N5" si="11">AH4</f>
+      <c r="N5" s="26">
+        <f t="shared" ref="N5:N6" si="11">AH5</f>
         <v>0.88432711890054905</v>
       </c>
-      <c r="O4" s="20">
-        <f t="shared" ref="O4:O5" si="12">AC4</f>
+      <c r="O5" s="27">
+        <f t="shared" ref="O5:O6" si="12">AC5</f>
         <v>113.056452248063</v>
       </c>
-      <c r="P4" s="20">
-        <f>(K4 * 20 + M4 * 1000) /G4</f>
+      <c r="P5" s="27">
+        <f>(K5 * 20 + M5 * 1000) /G5</f>
         <v>112.64651946584451</v>
       </c>
-      <c r="Q4" s="18">
-        <f t="shared" ref="Q4:Q5" si="13">E4/I4*1000</f>
+      <c r="Q5" s="25">
+        <f t="shared" ref="Q5:Q6" si="13">E5/I5*1000</f>
         <v>10.539630385505664</v>
       </c>
-      <c r="S4" t="s">
+      <c r="S5" t="s">
         <v>50</v>
       </c>
-      <c r="T4" t="s">
+      <c r="T5" t="s">
         <v>1</v>
       </c>
-      <c r="U4" t="s">
+      <c r="U5" t="s">
         <v>59</v>
       </c>
-      <c r="V4">
+      <c r="V5">
         <v>2662322</v>
       </c>
-      <c r="W4">
+      <c r="W5">
         <v>1054369.6604547901</v>
       </c>
-      <c r="X4">
+      <c r="X5">
         <v>241451.37207275201</v>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <v>482902.74414550501</v>
       </c>
-      <c r="Z4">
+      <c r="Z5">
         <v>-22908.903181728401</v>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <v>-5396438.4847435597</v>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <v>2450.0437441876402</v>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <v>113.056452248063</v>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <v>0.89510063316451904</v>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <v>0.89510063316451904</v>
       </c>
-      <c r="AF4">
+      <c r="AF5">
         <v>0.91843793158320297</v>
       </c>
-      <c r="AG4">
+      <c r="AG5">
         <v>0.90415194787729403</v>
       </c>
-      <c r="AH4">
+      <c r="AH5">
         <v>0.88432711890054905</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AI5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A5" s="28"/>
-      <c r="B5" s="15" t="str">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A6" s="32"/>
+      <c r="B6" s="14" t="str">
         <f t="shared" si="1"/>
         <v>[75,80)</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C6" s="15">
         <f t="shared" si="2"/>
         <v>2423.598</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D6" s="15">
         <f t="shared" si="0"/>
         <v>474.08745392027299</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E6" s="25">
         <f t="shared" si="0"/>
         <v>64.4578344689929</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F6" s="26">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G6" s="15">
         <f t="shared" si="4"/>
         <v>128.915668937985</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H6" s="26">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I6" s="15">
         <f t="shared" si="6"/>
         <v>5027.7031981967202</v>
       </c>
-      <c r="J5" s="19">
+      <c r="J6" s="26">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K6" s="15">
         <f t="shared" si="8"/>
         <v>597.53479213669596</v>
       </c>
-      <c r="L5" s="19">
+      <c r="L6" s="26">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="M5" s="20">
+      <c r="M6" s="27">
         <f t="shared" si="10"/>
         <v>1.5215653676954</v>
       </c>
-      <c r="N5" s="19">
+      <c r="N6" s="26">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="O5" s="20">
+      <c r="O6" s="27">
         <f t="shared" si="12"/>
         <v>112.15935273421699</v>
       </c>
-      <c r="P5" s="20">
-        <f>(K5 * 20 + M5 * 1000) /G5</f>
+      <c r="P6" s="27">
+        <f>(K6 * 20 + M6 * 1000) /G6</f>
         <v>104.50445102146709</v>
       </c>
-      <c r="Q5" s="18">
+      <c r="Q6" s="25">
         <f t="shared" si="13"/>
         <v>12.820532940789326</v>
       </c>
-      <c r="S5" t="s">
+      <c r="S6" t="s">
         <v>50</v>
       </c>
-      <c r="T5" t="s">
+      <c r="T6" t="s">
         <v>2</v>
       </c>
-      <c r="U5" t="s">
+      <c r="U6" t="s">
         <v>59</v>
       </c>
-      <c r="V5">
+      <c r="V6">
         <v>2423598</v>
       </c>
-      <c r="W5">
+      <c r="W6">
         <v>474087.45392027299</v>
       </c>
-      <c r="X5">
+      <c r="X6">
         <v>64457.8344689929</v>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <v>128915.668937985</v>
       </c>
-      <c r="Z5">
+      <c r="Z6">
         <v>-5027.7031981967202</v>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <v>-1521565.3676954</v>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <v>597.53479213669596</v>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <v>112.15935273421699</v>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <v>1</v>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <v>1</v>
       </c>
-      <c r="AF5">
+      <c r="AF6">
         <v>1</v>
       </c>
-      <c r="AG5">
+      <c r="AG6">
         <v>1</v>
       </c>
-      <c r="AH5">
+      <c r="AH6">
         <v>1</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AI6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21"/>
-      <c r="P6" s="21"/>
-      <c r="Q6" s="18"/>
-    </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="18"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="25"/>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="22" t="str">
-        <f>T8</f>
-        <v>[80,85)</v>
-      </c>
-      <c r="C8" s="23">
-        <f>V8/1000</f>
-        <v>1508.4970000000001</v>
-      </c>
-      <c r="D8" s="17">
-        <f>W8/1000</f>
-        <v>1076.1643642254198</v>
-      </c>
-      <c r="E8" s="18">
-        <f t="shared" ref="E8:E13" si="14">X8 / 1000</f>
-        <v>146.31735954425099</v>
-      </c>
-      <c r="F8" s="19">
-        <f t="shared" ref="F8:F13" si="15">AD8</f>
-        <v>1.2381184304386501</v>
-      </c>
-      <c r="G8" s="17">
-        <f t="shared" ref="G8:G13" si="16">Y8 / 1000</f>
-        <v>146.31735954425099</v>
-      </c>
-      <c r="H8" s="19">
-        <f t="shared" ref="H8:H13" si="17">AE8</f>
-        <v>1.1190592152193199</v>
-      </c>
-      <c r="I8" s="17">
-        <f t="shared" ref="I8:I13" si="18">-Z8</f>
-        <v>6708.3275629876898</v>
-      </c>
-      <c r="J8" s="19">
-        <f t="shared" ref="J8:J13" si="19">AF8</f>
-        <v>1.1088260484132999</v>
-      </c>
-      <c r="K8" s="17">
-        <f t="shared" ref="K8:K13" si="20">AB8</f>
-        <v>666.251075773612</v>
-      </c>
-      <c r="L8" s="19">
-        <f t="shared" ref="L8:L13" si="21">AG8</f>
-        <v>1.10687054323516</v>
-      </c>
-      <c r="M8" s="20">
-        <f t="shared" ref="M8:M13" si="22">-AA8/1000000</f>
-        <v>2.0280589322651998</v>
-      </c>
-      <c r="N8" s="19">
-        <f t="shared" ref="N8:N13" si="23">AH8</f>
-        <v>1.1541776809036499</v>
-      </c>
-      <c r="O8" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$8:K8)) * 20 + (SUM($M$3:$M$5) + SUM($M$8:M8)) * 1000) /(SUM($G$3:$G$5) + SUM($G$8:G8))</f>
-        <v>111.39020564710226</v>
-      </c>
-      <c r="P8" s="20">
-        <f>(K8 * 20 + M8 * 1000) /G8</f>
-        <v>104.92999939008729</v>
-      </c>
-      <c r="Q8" s="18">
-        <f t="shared" ref="Q8:Q13" si="24">E8/I8*1000</f>
-        <v>21.811302171876292</v>
-      </c>
-      <c r="S8" t="s">
-        <v>51</v>
-      </c>
-      <c r="T8" t="s">
-        <v>3</v>
-      </c>
-      <c r="U8" t="s">
-        <v>56</v>
-      </c>
-      <c r="V8">
-        <v>1508497</v>
-      </c>
-      <c r="W8">
-        <v>1076164.3642254199</v>
-      </c>
-      <c r="X8">
-        <v>146317.359544251</v>
-      </c>
-      <c r="Y8">
-        <v>146317.359544251</v>
-      </c>
-      <c r="Z8">
-        <v>-6708.3275629876898</v>
-      </c>
-      <c r="AA8">
-        <v>-2028058.9322652</v>
-      </c>
-      <c r="AB8">
-        <v>666.251075773612</v>
-      </c>
-      <c r="AC8">
-        <v>111.39020564710199</v>
-      </c>
-      <c r="AD8">
-        <v>1.2381184304386501</v>
-      </c>
-      <c r="AE8">
-        <v>1.1190592152193199</v>
-      </c>
-      <c r="AF8">
-        <v>1.1088260484132999</v>
-      </c>
-      <c r="AG8">
-        <v>1.10687054323516</v>
-      </c>
-      <c r="AH8">
-        <v>1.1541776809036499</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>61</v>
-      </c>
+      <c r="A8" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="30"/>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="20" t="str">
+        <f>T9</f>
+        <v>[80,85)</v>
+      </c>
+      <c r="C9" s="21">
+        <f>V9/1000</f>
+        <v>1508.4970000000001</v>
+      </c>
+      <c r="D9" s="15">
+        <f>W9/1000</f>
+        <v>1076.1643642254198</v>
+      </c>
+      <c r="E9" s="25">
+        <f t="shared" ref="E9:E14" si="14">X9 / 1000</f>
+        <v>146.31735954425099</v>
+      </c>
+      <c r="F9" s="26">
+        <f t="shared" ref="F9:F14" si="15">AD9</f>
+        <v>1.2381184304386501</v>
+      </c>
+      <c r="G9" s="15">
+        <f t="shared" ref="G9:G14" si="16">Y9 / 1000</f>
+        <v>146.31735954425099</v>
+      </c>
+      <c r="H9" s="26">
+        <f t="shared" ref="H9:H14" si="17">AE9</f>
+        <v>1.1190592152193199</v>
+      </c>
+      <c r="I9" s="15">
+        <f t="shared" ref="I9:I14" si="18">-Z9</f>
+        <v>6708.3275629876898</v>
+      </c>
+      <c r="J9" s="26">
+        <f t="shared" ref="J9:J14" si="19">AF9</f>
+        <v>1.1088260484132999</v>
+      </c>
+      <c r="K9" s="15">
+        <f t="shared" ref="K9:K14" si="20">AB9</f>
+        <v>666.251075773612</v>
+      </c>
+      <c r="L9" s="26">
+        <f t="shared" ref="L9:L14" si="21">AG9</f>
+        <v>1.10687054323516</v>
+      </c>
+      <c r="M9" s="27">
+        <f t="shared" ref="M9:M14" si="22">-AA9/1000000</f>
+        <v>2.0280589322651998</v>
+      </c>
+      <c r="N9" s="26">
+        <f t="shared" ref="N9:N14" si="23">AH9</f>
+        <v>1.1541776809036499</v>
+      </c>
+      <c r="O9" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$9:K9)) * 20 + (SUM($M$4:$M$6) + SUM($M$9:M9)) * 1000) /(SUM($G$4:$G$6) + SUM($G$9:G9))</f>
+        <v>111.39020564710226</v>
+      </c>
+      <c r="P9" s="27">
+        <f>(K9 * 20 + M9 * 1000) /G9</f>
+        <v>104.92999939008729</v>
+      </c>
+      <c r="Q9" s="25">
+        <f t="shared" ref="Q9:Q14" si="24">E9/I9*1000</f>
+        <v>21.811302171876292</v>
+      </c>
+      <c r="S9" t="s">
+        <v>51</v>
+      </c>
+      <c r="T9" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" t="s">
+        <v>56</v>
+      </c>
+      <c r="V9">
+        <v>1508497</v>
+      </c>
+      <c r="W9">
+        <v>1076164.3642254199</v>
+      </c>
+      <c r="X9">
+        <v>146317.359544251</v>
+      </c>
+      <c r="Y9">
+        <v>146317.359544251</v>
+      </c>
+      <c r="Z9">
+        <v>-6708.3275629876898</v>
+      </c>
+      <c r="AA9">
+        <v>-2028058.9322652</v>
+      </c>
+      <c r="AB9">
+        <v>666.251075773612</v>
+      </c>
+      <c r="AC9">
+        <v>111.39020564710199</v>
+      </c>
+      <c r="AD9">
+        <v>1.2381184304386501</v>
+      </c>
+      <c r="AE9">
+        <v>1.1190592152193199</v>
+      </c>
+      <c r="AF9">
+        <v>1.1088260484132999</v>
+      </c>
+      <c r="AG9">
+        <v>1.10687054323516</v>
+      </c>
+      <c r="AH9">
+        <v>1.1541776809036499</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="17">
-        <f t="shared" ref="D9:D13" si="25">W9/1000</f>
+      <c r="B10" s="20"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="15">
+        <f t="shared" ref="D10:D14" si="25">W10/1000</f>
         <v>432.33263577457899</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E10" s="25">
         <f t="shared" si="14"/>
         <v>58.780769754323998</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F10" s="26">
         <f t="shared" si="15"/>
         <v>1.3337788816487699</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G10" s="15">
         <f t="shared" si="16"/>
         <v>58.780769754323998</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H10" s="26">
         <f t="shared" si="17"/>
         <v>1.16688944082438</v>
       </c>
-      <c r="I9" s="17">
+      <c r="I10" s="15">
         <f t="shared" si="18"/>
         <v>2970.9802708871898</v>
       </c>
-      <c r="J9" s="19">
+      <c r="J10" s="26">
         <f t="shared" si="19"/>
         <v>1.15702286643668</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K10" s="15">
         <f t="shared" si="20"/>
         <v>393.47203395306099</v>
       </c>
-      <c r="L9" s="19">
+      <c r="L10" s="26">
         <f t="shared" si="21"/>
         <v>1.16998574341338</v>
       </c>
-      <c r="M9" s="20">
+      <c r="M10" s="27">
         <f t="shared" si="22"/>
         <v>1.1941161129870799</v>
       </c>
-      <c r="N9" s="19">
+      <c r="N10" s="26">
         <f t="shared" si="23"/>
         <v>1.2449571203474501</v>
       </c>
-      <c r="O9" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$8:K9)) * 20 + (SUM($M$3:$M$5) + SUM($M$8:M9)) * 1000) /(SUM($G$3:$G$5) + SUM($G$8:G9))</f>
+      <c r="O10" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$9:K10)) * 20 + (SUM($M$4:$M$6) + SUM($M$9:M10)) * 1000) /(SUM($G$4:$G$6) + SUM($G$9:G10))</f>
         <v>113.14465274852147</v>
       </c>
-      <c r="P9" s="20">
-        <f t="shared" ref="P9:P13" si="26">(K9 * 20 + M9 * 1000) /G9</f>
+      <c r="P10" s="27">
+        <f t="shared" ref="P10:P14" si="26">(K10 * 20 + M10 * 1000) /G10</f>
         <v>154.19255021548219</v>
       </c>
-      <c r="Q9" s="18">
+      <c r="Q10" s="25">
         <f t="shared" si="24"/>
         <v>19.784974787722494</v>
       </c>
-      <c r="S9" t="s">
+      <c r="S10" t="s">
         <v>52</v>
       </c>
-      <c r="T9" t="s">
+      <c r="T10" t="s">
         <v>3</v>
       </c>
-      <c r="U9" t="s">
+      <c r="U10" t="s">
         <v>57</v>
       </c>
-      <c r="V9">
+      <c r="V10">
         <v>1508497</v>
       </c>
-      <c r="W9">
+      <c r="W10">
         <v>432332.63577457902</v>
       </c>
-      <c r="X9">
+      <c r="X10">
         <v>58780.769754323999</v>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <v>58780.769754323999</v>
       </c>
-      <c r="Z9">
+      <c r="Z10">
         <v>-2970.9802708871898</v>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <v>-1194116.1129870799</v>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <v>393.47203395306099</v>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <v>113.144652748521</v>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <v>1.3337788816487699</v>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <v>1.16688944082438</v>
       </c>
-      <c r="AF9">
+      <c r="AF10">
         <v>1.15702286643668</v>
       </c>
-      <c r="AG9">
+      <c r="AG10">
         <v>1.16998574341338</v>
       </c>
-      <c r="AH9">
+      <c r="AH10">
         <v>1.2449571203474501</v>
       </c>
-      <c r="AI9" t="s">
+      <c r="AI10" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="22" t="str">
-        <f>T10</f>
+      <c r="B11" s="20" t="str">
+        <f>T11</f>
         <v>[85,90)</v>
       </c>
-      <c r="C10" s="23">
-        <f>V10/1000</f>
+      <c r="C11" s="21">
+        <f>V11/1000</f>
         <v>940.56899999999996</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D11" s="15">
         <f t="shared" si="25"/>
         <v>344.866124798366</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E11" s="25">
         <f t="shared" si="14"/>
         <v>46.888656095831699</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F11" s="26">
         <f t="shared" si="15"/>
         <v>1.41008598033954</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G11" s="15">
         <f t="shared" si="16"/>
         <v>46.888656095831699</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H11" s="26">
         <f t="shared" si="17"/>
         <v>1.2050429901697699</v>
       </c>
-      <c r="I10" s="17">
+      <c r="I11" s="15">
         <f t="shared" si="18"/>
         <v>2013.8918608971601</v>
       </c>
-      <c r="J10" s="19">
+      <c r="J11" s="26">
         <f t="shared" si="19"/>
         <v>1.18969328854939</v>
       </c>
-      <c r="K10" s="17">
+      <c r="K11" s="15">
         <f t="shared" si="20"/>
         <v>172.28852391461299</v>
       </c>
-      <c r="L10" s="19">
+      <c r="L11" s="26">
         <f t="shared" si="21"/>
         <v>1.19762182358415</v>
       </c>
-      <c r="M10" s="20">
+      <c r="M11" s="27">
         <f t="shared" si="22"/>
         <v>0.59842974890966394</v>
       </c>
-      <c r="N10" s="19">
+      <c r="N11" s="26">
         <f t="shared" si="23"/>
         <v>1.29045111926571</v>
       </c>
-      <c r="O10" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$8:K10)) * 20 + (SUM($M$3:$M$5) + SUM($M$8:M10)) * 1000) /(SUM($G$3:$G$5) + SUM($G$8:G10))</f>
+      <c r="O11" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$9:K11)) * 20 + (SUM($M$4:$M$6) + SUM($M$9:M11)) * 1000) /(SUM($G$4:$G$6) + SUM($G$9:G11))</f>
         <v>112.2931621188512</v>
       </c>
-      <c r="P10" s="20">
+      <c r="P11" s="27">
         <f t="shared" si="26"/>
         <v>86.251143964039628</v>
       </c>
-      <c r="Q10" s="18">
+      <c r="Q11" s="25">
         <f t="shared" si="24"/>
         <v>23.282608667450233</v>
       </c>
-      <c r="S10" t="s">
+      <c r="S11" t="s">
         <v>53</v>
-      </c>
-      <c r="T10" t="s">
-        <v>4</v>
-      </c>
-      <c r="U10" t="s">
-        <v>56</v>
-      </c>
-      <c r="V10">
-        <v>940569</v>
-      </c>
-      <c r="W10">
-        <v>344866.12479836599</v>
-      </c>
-      <c r="X10">
-        <v>46888.656095831699</v>
-      </c>
-      <c r="Y10">
-        <v>46888.656095831699</v>
-      </c>
-      <c r="Z10">
-        <v>-2013.8918608971601</v>
-      </c>
-      <c r="AA10">
-        <v>-598429.74890966399</v>
-      </c>
-      <c r="AB10">
-        <v>172.28852391461299</v>
-      </c>
-      <c r="AC10">
-        <v>112.293162118851</v>
-      </c>
-      <c r="AD10">
-        <v>1.41008598033954</v>
-      </c>
-      <c r="AE10">
-        <v>1.2050429901697699</v>
-      </c>
-      <c r="AF10">
-        <v>1.18969328854939</v>
-      </c>
-      <c r="AG10">
-        <v>1.19762182358415</v>
-      </c>
-      <c r="AH10">
-        <v>1.29045111926571</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="17">
-        <f t="shared" si="25"/>
-        <v>595.70287520163299</v>
-      </c>
-      <c r="E11" s="18">
-        <f t="shared" si="14"/>
-        <v>80.992899105293191</v>
-      </c>
-      <c r="F11" s="19">
-        <f t="shared" si="15"/>
-        <v>1.5418946876023101</v>
-      </c>
-      <c r="G11" s="17">
-        <f t="shared" si="16"/>
-        <v>80.992899105293191</v>
-      </c>
-      <c r="H11" s="19">
-        <f t="shared" si="17"/>
-        <v>1.27094734380115</v>
-      </c>
-      <c r="I11" s="17">
-        <f t="shared" si="18"/>
-        <v>2991.2900760042098</v>
-      </c>
-      <c r="J11" s="19">
-        <f t="shared" si="19"/>
-        <v>1.2382195830054901</v>
-      </c>
-      <c r="K11" s="17">
-        <f t="shared" si="20"/>
-        <v>429.17134849906301</v>
-      </c>
-      <c r="L11" s="19">
-        <f t="shared" si="21"/>
-        <v>1.26646340121583</v>
-      </c>
-      <c r="M11" s="20">
-        <f t="shared" si="22"/>
-        <v>1.50351979253798</v>
-      </c>
-      <c r="N11" s="19">
-        <f t="shared" si="23"/>
-        <v>1.4047521344474201</v>
-      </c>
-      <c r="O11" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$8:K11)) * 20 + (SUM($M$3:$M$5) + SUM($M$8:M11)) * 1000) /(SUM($G$3:$G$5) + SUM($G$8:G11))</f>
-        <v>112.92827424489134</v>
-      </c>
-      <c r="P11" s="20">
-        <f t="shared" si="26"/>
-        <v>124.54112488807085</v>
-      </c>
-      <c r="Q11" s="18">
-        <f t="shared" si="24"/>
-        <v>27.076243710033022</v>
-      </c>
-      <c r="S11" t="s">
-        <v>54</v>
       </c>
       <c r="T11" t="s">
         <v>4</v>
       </c>
       <c r="U11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V11">
         <v>940569</v>
       </c>
       <c r="W11">
-        <v>595702.87520163297</v>
+        <v>344866.12479836599</v>
       </c>
       <c r="X11">
-        <v>80992.899105293196</v>
+        <v>46888.656095831699</v>
       </c>
       <c r="Y11">
-        <v>80992.899105293196</v>
+        <v>46888.656095831699</v>
       </c>
       <c r="Z11">
-        <v>-2991.2900760042098</v>
+        <v>-2013.8918608971601</v>
       </c>
       <c r="AA11">
-        <v>-1503519.79253798</v>
+        <v>-598429.74890966399</v>
       </c>
       <c r="AB11">
-        <v>429.17134849906301</v>
+        <v>172.28852391461299</v>
       </c>
       <c r="AC11">
-        <v>112.928274244891</v>
+        <v>112.293162118851</v>
       </c>
       <c r="AD11">
-        <v>1.5418946876023101</v>
+        <v>1.41008598033954</v>
       </c>
       <c r="AE11">
-        <v>1.27094734380115</v>
+        <v>1.2050429901697699</v>
       </c>
       <c r="AF11">
-        <v>1.2382195830054901</v>
+        <v>1.18969328854939</v>
       </c>
       <c r="AG11">
-        <v>1.26646340121583</v>
+        <v>1.19762182358415</v>
       </c>
       <c r="AH11">
-        <v>1.4047521344474201</v>
+        <v>1.29045111926571</v>
       </c>
       <c r="AI11" t="s">
         <v>61</v>
@@ -1718,117 +1706,111 @@
       <c r="A12" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="15" t="str">
-        <f>T12</f>
-        <v>[90,95)</v>
-      </c>
-      <c r="C12" s="16">
-        <f>V12/1000</f>
-        <v>417.13799999999998</v>
-      </c>
-      <c r="D12" s="17">
+      <c r="B12" s="20"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="15">
         <f t="shared" si="25"/>
-        <v>417.13799999999998</v>
-      </c>
-      <c r="E12" s="18">
+        <v>595.70287520163299</v>
+      </c>
+      <c r="E12" s="25">
         <f t="shared" si="14"/>
-        <v>56.714878093459198</v>
-      </c>
-      <c r="F12" s="19">
+        <v>80.992899105293191</v>
+      </c>
+      <c r="F12" s="26">
         <f t="shared" si="15"/>
-        <v>1.63419308470433</v>
-      </c>
-      <c r="G12" s="17">
+        <v>1.5418946876023101</v>
+      </c>
+      <c r="G12" s="15">
         <f t="shared" si="16"/>
-        <v>56.714878093459198</v>
-      </c>
-      <c r="H12" s="19">
+        <v>80.992899105293191</v>
+      </c>
+      <c r="H12" s="26">
         <f t="shared" si="17"/>
-        <v>1.3170965423521599</v>
-      </c>
-      <c r="I12" s="17">
+        <v>1.27094734380115</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="18"/>
-        <v>1477.3691476014601</v>
-      </c>
-      <c r="J12" s="19">
+        <v>2991.2900760042098</v>
+      </c>
+      <c r="J12" s="26">
         <f t="shared" si="19"/>
-        <v>1.2621862490443201</v>
-      </c>
-      <c r="K12" s="17">
+        <v>1.2382195830054901</v>
+      </c>
+      <c r="K12" s="15">
         <f t="shared" si="20"/>
-        <v>222.88904099605199</v>
-      </c>
-      <c r="L12" s="19">
+        <v>429.17134849906301</v>
+      </c>
+      <c r="L12" s="26">
         <f t="shared" si="21"/>
-        <v>1.30221609829741</v>
-      </c>
-      <c r="M12" s="20">
+        <v>1.26646340121583</v>
+      </c>
+      <c r="M12" s="27">
         <f t="shared" si="22"/>
-        <v>0.87716270430148302</v>
-      </c>
-      <c r="N12" s="19">
+        <v>1.50351979253798</v>
+      </c>
+      <c r="N12" s="26">
         <f t="shared" si="23"/>
-        <v>1.47143605046821</v>
-      </c>
-      <c r="O12" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$8:K12)) * 20 + (SUM($M$3:$M$5) + SUM($M$8:M12)) * 1000) /(SUM($G$3:$G$5) + SUM($G$8:G12))</f>
-        <v>112.26736796704174</v>
-      </c>
-      <c r="P12" s="20">
+        <v>1.4047521344474201</v>
+      </c>
+      <c r="O12" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$9:K12)) * 20 + (SUM($M$4:$M$6) + SUM($M$9:M12)) * 1000) /(SUM($G$4:$G$6) + SUM($G$9:G12))</f>
+        <v>112.92827424489134</v>
+      </c>
+      <c r="P12" s="27">
         <f t="shared" si="26"/>
-        <v>94.066031763855449</v>
-      </c>
-      <c r="Q12" s="18">
+        <v>124.54112488807085</v>
+      </c>
+      <c r="Q12" s="25">
         <f t="shared" si="24"/>
-        <v>38.389104162312442</v>
+        <v>27.076243710033022</v>
       </c>
       <c r="S12" t="s">
         <v>54</v>
       </c>
       <c r="T12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U12" t="s">
         <v>57</v>
       </c>
       <c r="V12">
-        <v>417138</v>
+        <v>940569</v>
       </c>
       <c r="W12">
-        <v>417138</v>
+        <v>595702.87520163297</v>
       </c>
       <c r="X12">
-        <v>56714.8780934592</v>
+        <v>80992.899105293196</v>
       </c>
       <c r="Y12">
-        <v>56714.8780934592</v>
+        <v>80992.899105293196</v>
       </c>
       <c r="Z12">
-        <v>-1477.3691476014601</v>
+        <v>-2991.2900760042098</v>
       </c>
       <c r="AA12">
-        <v>-877162.704301483</v>
+        <v>-1503519.79253798</v>
       </c>
       <c r="AB12">
-        <v>222.88904099605199</v>
+        <v>429.17134849906301</v>
       </c>
       <c r="AC12">
-        <v>112.267367967041</v>
+        <v>112.928274244891</v>
       </c>
       <c r="AD12">
-        <v>1.63419308470433</v>
+        <v>1.5418946876023101</v>
       </c>
       <c r="AE12">
-        <v>1.3170965423521599</v>
+        <v>1.27094734380115</v>
       </c>
       <c r="AF12">
-        <v>1.2621862490443201</v>
+        <v>1.2382195830054901</v>
       </c>
       <c r="AG12">
-        <v>1.30221609829741</v>
+        <v>1.26646340121583</v>
       </c>
       <c r="AH12">
-        <v>1.47143605046821</v>
+        <v>1.4047521344474201</v>
       </c>
       <c r="AI12" t="s">
         <v>61</v>
@@ -1838,622 +1820,628 @@
       <c r="A13" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="15" t="str">
+      <c r="B13" s="14" t="str">
         <f>T13</f>
+        <v>[90,95)</v>
+      </c>
+      <c r="C13" s="15">
+        <f>V13/1000</f>
+        <v>417.13799999999998</v>
+      </c>
+      <c r="D13" s="15">
+        <f t="shared" si="25"/>
+        <v>417.13799999999998</v>
+      </c>
+      <c r="E13" s="25">
+        <f t="shared" si="14"/>
+        <v>56.714878093459198</v>
+      </c>
+      <c r="F13" s="26">
+        <f t="shared" si="15"/>
+        <v>1.63419308470433</v>
+      </c>
+      <c r="G13" s="15">
+        <f t="shared" si="16"/>
+        <v>56.714878093459198</v>
+      </c>
+      <c r="H13" s="26">
+        <f t="shared" si="17"/>
+        <v>1.3170965423521599</v>
+      </c>
+      <c r="I13" s="15">
+        <f t="shared" si="18"/>
+        <v>1477.3691476014601</v>
+      </c>
+      <c r="J13" s="26">
+        <f t="shared" si="19"/>
+        <v>1.2621862490443201</v>
+      </c>
+      <c r="K13" s="15">
+        <f t="shared" si="20"/>
+        <v>222.88904099605199</v>
+      </c>
+      <c r="L13" s="26">
+        <f t="shared" si="21"/>
+        <v>1.30221609829741</v>
+      </c>
+      <c r="M13" s="27">
+        <f t="shared" si="22"/>
+        <v>0.87716270430148302</v>
+      </c>
+      <c r="N13" s="26">
+        <f t="shared" si="23"/>
+        <v>1.47143605046821</v>
+      </c>
+      <c r="O13" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$9:K13)) * 20 + (SUM($M$4:$M$6) + SUM($M$9:M13)) * 1000) /(SUM($G$4:$G$6) + SUM($G$9:G13))</f>
+        <v>112.26736796704174</v>
+      </c>
+      <c r="P13" s="27">
+        <f t="shared" si="26"/>
+        <v>94.066031763855449</v>
+      </c>
+      <c r="Q13" s="25">
+        <f t="shared" si="24"/>
+        <v>38.389104162312442</v>
+      </c>
+      <c r="S13" t="s">
+        <v>54</v>
+      </c>
+      <c r="T13" t="s">
+        <v>5</v>
+      </c>
+      <c r="U13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V13">
+        <v>417138</v>
+      </c>
+      <c r="W13">
+        <v>417138</v>
+      </c>
+      <c r="X13">
+        <v>56714.8780934592</v>
+      </c>
+      <c r="Y13">
+        <v>56714.8780934592</v>
+      </c>
+      <c r="Z13">
+        <v>-1477.3691476014601</v>
+      </c>
+      <c r="AA13">
+        <v>-877162.704301483</v>
+      </c>
+      <c r="AB13">
+        <v>222.88904099605199</v>
+      </c>
+      <c r="AC13">
+        <v>112.267367967041</v>
+      </c>
+      <c r="AD13">
+        <v>1.63419308470433</v>
+      </c>
+      <c r="AE13">
+        <v>1.3170965423521599</v>
+      </c>
+      <c r="AF13">
+        <v>1.2621862490443201</v>
+      </c>
+      <c r="AG13">
+        <v>1.30221609829741</v>
+      </c>
+      <c r="AH13">
+        <v>1.47143605046821</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="14" t="str">
+        <f>T14</f>
         <v>[95,100)</v>
       </c>
-      <c r="C13" s="16">
-        <f>V13/1000</f>
+      <c r="C14" s="15">
+        <f>V14/1000</f>
         <v>109.06399999999999</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D14" s="15">
         <f t="shared" si="25"/>
         <v>109.06399999999999</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E14" s="25">
         <f t="shared" si="14"/>
         <v>14.8285494593756</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F14" s="26">
         <f t="shared" si="15"/>
         <v>1.65832522414388</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G14" s="15">
         <f t="shared" si="16"/>
         <v>14.8285494593756</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H14" s="26">
         <f t="shared" si="17"/>
         <v>1.32916261207194</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I14" s="15">
         <f t="shared" si="18"/>
         <v>242.50151599851301</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J14" s="26">
         <f t="shared" si="19"/>
         <v>1.2661202372809599</v>
       </c>
-      <c r="K13" s="17">
+      <c r="K14" s="15">
         <f t="shared" si="20"/>
         <v>35.483222543958902</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L14" s="26">
         <f t="shared" si="21"/>
         <v>1.3079078133383299</v>
       </c>
-      <c r="M13" s="20">
+      <c r="M14" s="27">
         <f t="shared" si="22"/>
         <v>0.147012741783423</v>
       </c>
-      <c r="N13" s="19">
+      <c r="N14" s="26">
         <f t="shared" si="23"/>
         <v>1.4826122955126</v>
       </c>
-      <c r="O13" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$8:K13)) * 20 + (SUM($M$3:$M$5) + SUM($M$8:M13)) * 1000) /(SUM($G$3:$G$5) + SUM($G$8:G13))</f>
+      <c r="O14" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$9:K14)) * 20 + (SUM($M$4:$M$6) + SUM($M$9:M14)) * 1000) /(SUM($G$4:$G$6) + SUM($G$9:G14))</f>
         <v>111.77266319120876</v>
       </c>
-      <c r="P13" s="20">
+      <c r="P14" s="27">
         <f t="shared" si="26"/>
         <v>57.772150607823107</v>
       </c>
-      <c r="Q13" s="18">
+      <c r="Q14" s="25">
         <f t="shared" si="24"/>
         <v>61.148275293530645</v>
       </c>
-      <c r="S13" t="s">
+      <c r="S14" t="s">
         <v>55</v>
       </c>
-      <c r="T13" t="s">
+      <c r="T14" t="s">
         <v>28</v>
       </c>
-      <c r="U13" t="s">
+      <c r="U14" t="s">
         <v>57</v>
       </c>
-      <c r="V13">
+      <c r="V14">
         <v>109064</v>
       </c>
-      <c r="W13">
+      <c r="W14">
         <v>109064</v>
       </c>
-      <c r="X13">
+      <c r="X14">
         <v>14828.549459375599</v>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <v>14828.549459375599</v>
       </c>
-      <c r="Z13">
+      <c r="Z14">
         <v>-242.50151599851301</v>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <v>-147012.741783423</v>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <v>35.483222543958902</v>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <v>111.772663191208</v>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <v>1.65832522414388</v>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <v>1.32916261207194</v>
       </c>
-      <c r="AF13">
+      <c r="AF14">
         <v>1.2661202372809599</v>
       </c>
-      <c r="AG13">
+      <c r="AG14">
         <v>1.3079078133383299</v>
       </c>
-      <c r="AH13">
+      <c r="AH14">
         <v>1.4826122955126</v>
       </c>
-      <c r="AI13" t="s">
+      <c r="AI14" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="20"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="20"/>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="18"/>
-    </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="18"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="25"/>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="23">
-        <v>1508.4970000000001</v>
-      </c>
-      <c r="D16" s="17">
-        <f t="shared" ref="D16:D21" si="27">W16/1000</f>
-        <v>1076.1643642254198</v>
-      </c>
-      <c r="E16" s="18">
-        <f t="shared" ref="E16:E21" si="28">X16 / 1000</f>
-        <v>146.31735954425099</v>
-      </c>
-      <c r="F16" s="19">
-        <f t="shared" ref="F16:F21" si="29">AD16</f>
-        <v>1.2381184304386501</v>
-      </c>
-      <c r="G16" s="17">
-        <f t="shared" ref="G16:G21" si="30">Y16 / 1000</f>
-        <v>292.63471908850198</v>
-      </c>
-      <c r="H16" s="19">
-        <f t="shared" ref="H16:H21" si="31">AE16</f>
-        <v>1.2381184304386501</v>
-      </c>
-      <c r="I16" s="17">
-        <f t="shared" ref="I16:I21" si="32">-Z16</f>
-        <v>8227.6866740854493</v>
-      </c>
-      <c r="J16" s="19">
-        <f t="shared" ref="J16:J21" si="33">AF16</f>
-        <v>1.13347389791513</v>
-      </c>
-      <c r="K16" s="17">
-        <f t="shared" ref="K16:K21" si="34">AB16</f>
-        <v>819.70537271405999</v>
-      </c>
-      <c r="L16" s="19">
-        <f t="shared" ref="L16:L21" si="35">AG16</f>
-        <v>1.1314855039791301</v>
-      </c>
-      <c r="M16" s="20">
-        <f t="shared" ref="M16:M21" si="36">-AA16/1000000</f>
-        <v>2.48039997451226</v>
-      </c>
-      <c r="N16" s="19">
-        <f t="shared" ref="N16:N21" si="37">AH16</f>
-        <v>1.1885656820419099</v>
-      </c>
-      <c r="O16" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$16:K16)) * 20 + (SUM($M$3:$M$5) + SUM($M$16:M16)) * 1000) /(SUM($G$3:$G$5) + SUM($G$16:G16))</f>
-        <v>102.99308764053391</v>
-      </c>
-      <c r="P16" s="20">
-        <f>(K16 * 20 + M16 * 1000) /G16</f>
-        <v>64.498523919457455</v>
-      </c>
-      <c r="Q16" s="18">
-        <f t="shared" ref="Q16:Q21" si="38">E16/I16*1000</f>
-        <v>17.783535681433193</v>
-      </c>
-      <c r="S16" t="s">
-        <v>51</v>
-      </c>
-      <c r="T16" t="s">
-        <v>3</v>
-      </c>
-      <c r="U16" t="s">
-        <v>58</v>
-      </c>
-      <c r="V16">
-        <v>1508497</v>
-      </c>
-      <c r="W16">
-        <v>1076164.3642254199</v>
-      </c>
-      <c r="X16">
-        <v>146317.359544251</v>
-      </c>
-      <c r="Y16">
-        <v>292634.719088502</v>
-      </c>
-      <c r="Z16">
-        <v>-8227.6866740854493</v>
-      </c>
-      <c r="AA16">
-        <v>-2480399.9745122599</v>
-      </c>
-      <c r="AB16">
-        <v>819.70537271405999</v>
-      </c>
-      <c r="AC16">
-        <v>102.99308764053301</v>
-      </c>
-      <c r="AD16">
-        <v>1.2381184304386501</v>
-      </c>
-      <c r="AE16">
-        <v>1.2381184304386501</v>
-      </c>
-      <c r="AF16">
-        <v>1.13347389791513</v>
-      </c>
-      <c r="AG16">
-        <v>1.1314855039791301</v>
-      </c>
-      <c r="AH16">
-        <v>1.1885656820419099</v>
-      </c>
-      <c r="AI16" t="s">
-        <v>62</v>
-      </c>
+      <c r="A16" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="30"/>
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="21">
+        <v>1508.4970000000001</v>
+      </c>
+      <c r="D17" s="15">
+        <f t="shared" ref="D17:D22" si="27">W17/1000</f>
+        <v>1076.1643642254198</v>
+      </c>
+      <c r="E17" s="25">
+        <f t="shared" ref="E17:E22" si="28">X17 / 1000</f>
+        <v>146.31735954425099</v>
+      </c>
+      <c r="F17" s="26">
+        <f t="shared" ref="F17:F22" si="29">AD17</f>
+        <v>1.2381184304386501</v>
+      </c>
+      <c r="G17" s="15">
+        <f t="shared" ref="G17:G22" si="30">Y17 / 1000</f>
+        <v>292.63471908850198</v>
+      </c>
+      <c r="H17" s="26">
+        <f t="shared" ref="H17:H22" si="31">AE17</f>
+        <v>1.2381184304386501</v>
+      </c>
+      <c r="I17" s="15">
+        <f t="shared" ref="I17:I22" si="32">-Z17</f>
+        <v>8227.6866740854493</v>
+      </c>
+      <c r="J17" s="26">
+        <f t="shared" ref="J17:J22" si="33">AF17</f>
+        <v>1.13347389791513</v>
+      </c>
+      <c r="K17" s="15">
+        <f t="shared" ref="K17:K22" si="34">AB17</f>
+        <v>819.70537271405999</v>
+      </c>
+      <c r="L17" s="26">
+        <f t="shared" ref="L17:L22" si="35">AG17</f>
+        <v>1.1314855039791301</v>
+      </c>
+      <c r="M17" s="27">
+        <f t="shared" ref="M17:M22" si="36">-AA17/1000000</f>
+        <v>2.48039997451226</v>
+      </c>
+      <c r="N17" s="26">
+        <f t="shared" ref="N17:N22" si="37">AH17</f>
+        <v>1.1885656820419099</v>
+      </c>
+      <c r="O17" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$17:K17)) * 20 + (SUM($M$4:$M$6) + SUM($M$17:M17)) * 1000) /(SUM($G$4:$G$6) + SUM($G$17:G17))</f>
+        <v>102.99308764053391</v>
+      </c>
+      <c r="P17" s="27">
+        <f>(K17 * 20 + M17 * 1000) /G17</f>
+        <v>64.498523919457455</v>
+      </c>
+      <c r="Q17" s="25">
+        <f t="shared" ref="Q17:Q22" si="38">E17/I17*1000</f>
+        <v>17.783535681433193</v>
+      </c>
+      <c r="S17" t="s">
+        <v>51</v>
+      </c>
+      <c r="T17" t="s">
+        <v>3</v>
+      </c>
+      <c r="U17" t="s">
+        <v>58</v>
+      </c>
+      <c r="V17">
+        <v>1508497</v>
+      </c>
+      <c r="W17">
+        <v>1076164.3642254199</v>
+      </c>
+      <c r="X17">
+        <v>146317.359544251</v>
+      </c>
+      <c r="Y17">
+        <v>292634.719088502</v>
+      </c>
+      <c r="Z17">
+        <v>-8227.6866740854493</v>
+      </c>
+      <c r="AA17">
+        <v>-2480399.9745122599</v>
+      </c>
+      <c r="AB17">
+        <v>819.70537271405999</v>
+      </c>
+      <c r="AC17">
+        <v>102.99308764053301</v>
+      </c>
+      <c r="AD17">
+        <v>1.2381184304386501</v>
+      </c>
+      <c r="AE17">
+        <v>1.2381184304386501</v>
+      </c>
+      <c r="AF17">
+        <v>1.13347389791513</v>
+      </c>
+      <c r="AG17">
+        <v>1.1314855039791301</v>
+      </c>
+      <c r="AH17">
+        <v>1.1885656820419099</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="17">
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="15">
         <f t="shared" si="27"/>
         <v>432.33263577457899</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E18" s="25">
         <f t="shared" si="28"/>
         <v>58.780769754323998</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F18" s="26">
         <f t="shared" si="29"/>
         <v>1.3337788816487699</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G18" s="15">
         <f t="shared" si="30"/>
         <v>117.561539508648</v>
       </c>
-      <c r="H17" s="19">
+      <c r="H18" s="26">
         <f t="shared" si="31"/>
         <v>1.3337788816487699</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I18" s="15">
         <f t="shared" si="32"/>
         <v>3401.68027509177</v>
       </c>
-      <c r="J17" s="19">
+      <c r="J18" s="26">
         <f t="shared" si="33"/>
         <v>1.18865775988786</v>
       </c>
-      <c r="K17" s="17">
+      <c r="K18" s="15">
         <f t="shared" si="34"/>
         <v>450.01264339643399</v>
       </c>
-      <c r="L17" s="19">
+      <c r="L18" s="26">
         <f t="shared" si="35"/>
         <v>1.2036701463928401</v>
       </c>
-      <c r="M17" s="20">
+      <c r="M18" s="27">
         <f t="shared" si="36"/>
         <v>1.36683611281877</v>
       </c>
-      <c r="N17" s="19">
+      <c r="N18" s="26">
         <f t="shared" si="37"/>
         <v>1.2924756911136801</v>
       </c>
-      <c r="O17" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$16:K17)) * 20 + (SUM($M$3:$M$5) + SUM($M$16:M17)) * 1000) /(SUM($G$3:$G$5) + SUM($G$16:G17))</f>
+      <c r="O18" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$17:K18)) * 20 + (SUM($M$4:$M$6) + SUM($M$17:M18)) * 1000) /(SUM($G$4:$G$6) + SUM($G$17:G18))</f>
         <v>101.93098529169602</v>
       </c>
-      <c r="P17" s="20">
-        <f t="shared" ref="P17:P21" si="39">(K17 * 20 + M17 * 1000) /G17</f>
+      <c r="P18" s="27">
+        <f t="shared" ref="P18:P22" si="39">(K18 * 20 + M18 * 1000) /G18</f>
         <v>88.184358796907659</v>
       </c>
-      <c r="Q17" s="18">
+      <c r="Q18" s="25">
         <f t="shared" si="38"/>
         <v>17.279921979950988</v>
       </c>
-      <c r="S17" t="s">
+      <c r="S18" t="s">
         <v>52</v>
       </c>
-      <c r="T17" t="s">
+      <c r="T18" t="s">
         <v>3</v>
       </c>
-      <c r="U17" t="s">
+      <c r="U18" t="s">
         <v>59</v>
       </c>
-      <c r="V17">
+      <c r="V18">
         <v>1508497</v>
       </c>
-      <c r="W17">
+      <c r="W18">
         <v>432332.63577457902</v>
       </c>
-      <c r="X17">
+      <c r="X18">
         <v>58780.769754323999</v>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <v>117561.539508648</v>
       </c>
-      <c r="Z17">
+      <c r="Z18">
         <v>-3401.68027509177</v>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <v>-1366836.1128187701</v>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <v>450.01264339643399</v>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <v>101.930985291696</v>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <v>1.3337788816487699</v>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <v>1.3337788816487699</v>
       </c>
-      <c r="AF17">
+      <c r="AF18">
         <v>1.18865775988786</v>
       </c>
-      <c r="AG17">
+      <c r="AG18">
         <v>1.2036701463928401</v>
       </c>
-      <c r="AH17">
+      <c r="AH18">
         <v>1.2924756911136801</v>
       </c>
-      <c r="AI17" t="s">
+      <c r="AI18" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="22" t="str">
-        <f>T18</f>
+      <c r="B19" s="20" t="str">
+        <f>T19</f>
         <v>[85,90)</v>
       </c>
-      <c r="C18" s="23">
+      <c r="C19" s="21">
         <v>940.56899999999996</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D19" s="15">
         <f t="shared" si="27"/>
         <v>344.866124798366</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E19" s="25">
         <f t="shared" si="28"/>
         <v>46.888656095831699</v>
       </c>
-      <c r="F18" s="19">
+      <c r="F19" s="26">
         <f t="shared" si="29"/>
         <v>1.41008598033954</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G19" s="15">
         <f t="shared" si="30"/>
         <v>93.777312191663498</v>
       </c>
-      <c r="H18" s="19">
+      <c r="H19" s="26">
         <f t="shared" si="31"/>
         <v>1.41008598033954</v>
       </c>
-      <c r="I18" s="17">
+      <c r="I19" s="15">
         <f t="shared" si="32"/>
         <v>2446.1601279562801</v>
       </c>
-      <c r="J18" s="19">
+      <c r="J19" s="26">
         <f t="shared" si="33"/>
         <v>1.2283406671418799</v>
       </c>
-      <c r="K18" s="17">
+      <c r="K19" s="15">
         <f t="shared" si="34"/>
         <v>210.052717532841</v>
       </c>
-      <c r="L18" s="19">
+      <c r="L19" s="26">
         <f t="shared" si="35"/>
         <v>1.2373638226164601</v>
       </c>
-      <c r="M18" s="20">
+      <c r="M19" s="27">
         <f t="shared" si="36"/>
         <v>0.72697001475812495</v>
       </c>
-      <c r="N18" s="19">
+      <c r="N19" s="26">
         <f t="shared" si="37"/>
         <v>1.34774161518459</v>
       </c>
-      <c r="O18" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$16:K18)) * 20 + (SUM($M$3:$M$5) + SUM($M$16:M18)) * 1000) /(SUM($G$3:$G$5) + SUM($G$16:G18))</f>
+      <c r="O19" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$17:K19)) * 20 + (SUM($M$4:$M$6) + SUM($M$17:M19)) * 1000) /(SUM($G$4:$G$6) + SUM($G$17:G19))</f>
         <v>99.258738266940654</v>
       </c>
-      <c r="P18" s="20">
+      <c r="P19" s="27">
         <f t="shared" si="39"/>
         <v>52.550283754592733</v>
       </c>
-      <c r="Q18" s="18">
+      <c r="Q19" s="25">
         <f t="shared" si="38"/>
         <v>19.168269305005097</v>
       </c>
-      <c r="S18" t="s">
+      <c r="S19" t="s">
         <v>53</v>
-      </c>
-      <c r="T18" t="s">
-        <v>4</v>
-      </c>
-      <c r="U18" t="s">
-        <v>58</v>
-      </c>
-      <c r="V18">
-        <v>940569</v>
-      </c>
-      <c r="W18">
-        <v>344866.12479836599</v>
-      </c>
-      <c r="X18">
-        <v>46888.656095831699</v>
-      </c>
-      <c r="Y18">
-        <v>93777.312191663499</v>
-      </c>
-      <c r="Z18">
-        <v>-2446.1601279562801</v>
-      </c>
-      <c r="AA18">
-        <v>-726970.01475812495</v>
-      </c>
-      <c r="AB18">
-        <v>210.052717532841</v>
-      </c>
-      <c r="AC18">
-        <v>99.258738266940696</v>
-      </c>
-      <c r="AD18">
-        <v>1.41008598033954</v>
-      </c>
-      <c r="AE18">
-        <v>1.41008598033954</v>
-      </c>
-      <c r="AF18">
-        <v>1.2283406671418799</v>
-      </c>
-      <c r="AG18">
-        <v>1.2373638226164601</v>
-      </c>
-      <c r="AH18">
-        <v>1.34774161518459</v>
-      </c>
-      <c r="AI18" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="17">
-        <f t="shared" si="27"/>
-        <v>595.70287520163299</v>
-      </c>
-      <c r="E19" s="18">
-        <f t="shared" si="28"/>
-        <v>80.992899105293191</v>
-      </c>
-      <c r="F19" s="19">
-        <f t="shared" si="29"/>
-        <v>1.5418946876023101</v>
-      </c>
-      <c r="G19" s="17">
-        <f t="shared" si="30"/>
-        <v>161.98579821058601</v>
-      </c>
-      <c r="H19" s="19">
-        <f t="shared" si="31"/>
-        <v>1.5418946876023101</v>
-      </c>
-      <c r="I19" s="17">
-        <f t="shared" si="32"/>
-        <v>3421.9017297001901</v>
-      </c>
-      <c r="J19" s="19">
-        <f t="shared" si="33"/>
-        <v>1.2838525722784999</v>
-      </c>
-      <c r="K19" s="17">
-        <f t="shared" si="34"/>
-        <v>489.89476123665298</v>
-      </c>
-      <c r="L19" s="19">
-        <f t="shared" si="35"/>
-        <v>1.31594578843262</v>
-      </c>
-      <c r="M19" s="20">
-        <f t="shared" si="36"/>
-        <v>1.71789924427458</v>
-      </c>
-      <c r="N19" s="19">
-        <f t="shared" si="37"/>
-        <v>1.4783402468587501</v>
-      </c>
-      <c r="O19" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$16:K19)) * 20 + (SUM($M$3:$M$5) + SUM($M$16:M19)) * 1000) /(SUM($G$3:$G$5) + SUM($G$16:G19))</f>
-        <v>96.850854852038054</v>
-      </c>
-      <c r="P19" s="20">
-        <f t="shared" si="39"/>
-        <v>71.091383295446619</v>
-      </c>
-      <c r="Q19" s="18">
-        <f t="shared" si="38"/>
-        <v>23.668972841131058</v>
-      </c>
-      <c r="S19" t="s">
-        <v>54</v>
       </c>
       <c r="T19" t="s">
         <v>4</v>
       </c>
       <c r="U19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V19">
         <v>940569</v>
       </c>
       <c r="W19">
-        <v>595702.87520163297</v>
+        <v>344866.12479836599</v>
       </c>
       <c r="X19">
-        <v>80992.899105293196</v>
+        <v>46888.656095831699</v>
       </c>
       <c r="Y19">
-        <v>161985.79821058601</v>
+        <v>93777.312191663499</v>
       </c>
       <c r="Z19">
-        <v>-3421.9017297001901</v>
+        <v>-2446.1601279562801</v>
       </c>
       <c r="AA19">
-        <v>-1717899.2442745799</v>
+        <v>-726970.01475812495</v>
       </c>
       <c r="AB19">
-        <v>489.89476123665298</v>
+        <v>210.052717532841</v>
       </c>
       <c r="AC19">
-        <v>96.850854852037997</v>
+        <v>99.258738266940696</v>
       </c>
       <c r="AD19">
-        <v>1.5418946876023101</v>
+        <v>1.41008598033954</v>
       </c>
       <c r="AE19">
-        <v>1.5418946876023101</v>
+        <v>1.41008598033954</v>
       </c>
       <c r="AF19">
-        <v>1.2838525722784999</v>
+        <v>1.2283406671418799</v>
       </c>
       <c r="AG19">
-        <v>1.31594578843262</v>
+        <v>1.2373638226164601</v>
       </c>
       <c r="AH19">
-        <v>1.4783402468587501</v>
+        <v>1.34774161518459</v>
       </c>
       <c r="AI19" t="s">
         <v>62</v>
@@ -2463,116 +2451,111 @@
       <c r="A20" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="15" t="str">
-        <f>T20</f>
-        <v>[90,95)</v>
-      </c>
-      <c r="C20" s="16">
-        <v>417.13799999999998</v>
-      </c>
-      <c r="D20" s="17">
+      <c r="B20" s="20"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="15">
         <f t="shared" si="27"/>
-        <v>417.13799999999998</v>
-      </c>
-      <c r="E20" s="18">
+        <v>595.70287520163299</v>
+      </c>
+      <c r="E20" s="25">
         <f t="shared" si="28"/>
-        <v>56.714878093459198</v>
-      </c>
-      <c r="F20" s="19">
+        <v>80.992899105293191</v>
+      </c>
+      <c r="F20" s="26">
         <f t="shared" si="29"/>
-        <v>1.63419308470433</v>
-      </c>
-      <c r="G20" s="17">
+        <v>1.5418946876023101</v>
+      </c>
+      <c r="G20" s="15">
         <f t="shared" si="30"/>
-        <v>113.42975618691801</v>
-      </c>
-      <c r="H20" s="19">
+        <v>161.98579821058601</v>
+      </c>
+      <c r="H20" s="26">
         <f t="shared" si="31"/>
-        <v>1.63419308470433</v>
-      </c>
-      <c r="I20" s="17">
+        <v>1.5418946876023101</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="32"/>
-        <v>1687.40184965618</v>
-      </c>
-      <c r="J20" s="19">
+        <v>3421.9017297001901</v>
+      </c>
+      <c r="J20" s="26">
         <f t="shared" si="33"/>
-        <v>1.31122650022987</v>
-      </c>
-      <c r="K20" s="17">
+        <v>1.2838525722784999</v>
+      </c>
+      <c r="K20" s="15">
         <f t="shared" si="34"/>
-        <v>254.776716327858</v>
-      </c>
-      <c r="L20" s="19">
+        <v>489.89476123665298</v>
+      </c>
+      <c r="L20" s="26">
         <f t="shared" si="35"/>
-        <v>1.35681345389344</v>
-      </c>
-      <c r="M20" s="20">
+        <v>1.31594578843262</v>
+      </c>
+      <c r="M20" s="27">
         <f t="shared" si="36"/>
-        <v>1.0028080909625301</v>
-      </c>
-      <c r="N20" s="19">
+        <v>1.71789924427458</v>
+      </c>
+      <c r="N20" s="26">
         <f t="shared" si="37"/>
-        <v>1.5545760126919099</v>
-      </c>
-      <c r="O20" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$16:K20)) * 20 + (SUM($M$3:$M$5) + SUM($M$16:M20)) * 1000) /(SUM($G$3:$G$5) + SUM($G$16:G20))</f>
-        <v>94.417283829464196</v>
-      </c>
-      <c r="P20" s="20">
+        <v>1.4783402468587501</v>
+      </c>
+      <c r="O20" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$17:K20)) * 20 + (SUM($M$4:$M$6) + SUM($M$17:M20)) * 1000) /(SUM($G$4:$G$6) + SUM($G$17:G20))</f>
+        <v>96.850854852038054</v>
+      </c>
+      <c r="P20" s="27">
         <f t="shared" si="39"/>
-        <v>53.763162529154933</v>
-      </c>
-      <c r="Q20" s="18">
+        <v>71.091383295446619</v>
+      </c>
+      <c r="Q20" s="25">
         <f t="shared" si="38"/>
-        <v>33.610771556885069</v>
+        <v>23.668972841131058</v>
       </c>
       <c r="S20" t="s">
         <v>54</v>
       </c>
       <c r="T20" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U20" t="s">
         <v>59</v>
       </c>
       <c r="V20">
-        <v>417138</v>
+        <v>940569</v>
       </c>
       <c r="W20">
-        <v>417138</v>
+        <v>595702.87520163297</v>
       </c>
       <c r="X20">
-        <v>56714.8780934592</v>
+        <v>80992.899105293196</v>
       </c>
       <c r="Y20">
-        <v>113429.75618691801</v>
+        <v>161985.79821058601</v>
       </c>
       <c r="Z20">
-        <v>-1687.40184965618</v>
+        <v>-3421.9017297001901</v>
       </c>
       <c r="AA20">
-        <v>-1002808.09096253</v>
+        <v>-1717899.2442745799</v>
       </c>
       <c r="AB20">
-        <v>254.776716327858</v>
+        <v>489.89476123665298</v>
       </c>
       <c r="AC20">
-        <v>94.417283829464196</v>
+        <v>96.850854852037997</v>
       </c>
       <c r="AD20">
-        <v>1.63419308470433</v>
+        <v>1.5418946876023101</v>
       </c>
       <c r="AE20">
-        <v>1.63419308470433</v>
+        <v>1.5418946876023101</v>
       </c>
       <c r="AF20">
-        <v>1.31122650022987</v>
+        <v>1.2838525722784999</v>
       </c>
       <c r="AG20">
-        <v>1.35681345389344</v>
+        <v>1.31594578843262</v>
       </c>
       <c r="AH20">
-        <v>1.5545760126919099</v>
+        <v>1.4783402468587501</v>
       </c>
       <c r="AI20" t="s">
         <v>62</v>
@@ -2582,627 +2565,632 @@
       <c r="A21" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="15" t="str">
+      <c r="B21" s="14" t="str">
         <f>T21</f>
+        <v>[90,95)</v>
+      </c>
+      <c r="C21" s="15">
+        <v>417.13799999999998</v>
+      </c>
+      <c r="D21" s="15">
+        <f t="shared" si="27"/>
+        <v>417.13799999999998</v>
+      </c>
+      <c r="E21" s="25">
+        <f t="shared" si="28"/>
+        <v>56.714878093459198</v>
+      </c>
+      <c r="F21" s="26">
+        <f t="shared" si="29"/>
+        <v>1.63419308470433</v>
+      </c>
+      <c r="G21" s="15">
+        <f t="shared" si="30"/>
+        <v>113.42975618691801</v>
+      </c>
+      <c r="H21" s="26">
+        <f t="shared" si="31"/>
+        <v>1.63419308470433</v>
+      </c>
+      <c r="I21" s="15">
+        <f t="shared" si="32"/>
+        <v>1687.40184965618</v>
+      </c>
+      <c r="J21" s="26">
+        <f t="shared" si="33"/>
+        <v>1.31122650022987</v>
+      </c>
+      <c r="K21" s="15">
+        <f t="shared" si="34"/>
+        <v>254.776716327858</v>
+      </c>
+      <c r="L21" s="26">
+        <f t="shared" si="35"/>
+        <v>1.35681345389344</v>
+      </c>
+      <c r="M21" s="27">
+        <f t="shared" si="36"/>
+        <v>1.0028080909625301</v>
+      </c>
+      <c r="N21" s="26">
+        <f t="shared" si="37"/>
+        <v>1.5545760126919099</v>
+      </c>
+      <c r="O21" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$17:K21)) * 20 + (SUM($M$4:$M$6) + SUM($M$17:M21)) * 1000) /(SUM($G$4:$G$6) + SUM($G$17:G21))</f>
+        <v>94.417283829464196</v>
+      </c>
+      <c r="P21" s="27">
+        <f t="shared" si="39"/>
+        <v>53.763162529154933</v>
+      </c>
+      <c r="Q21" s="25">
+        <f t="shared" si="38"/>
+        <v>33.610771556885069</v>
+      </c>
+      <c r="S21" t="s">
+        <v>54</v>
+      </c>
+      <c r="T21" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" t="s">
+        <v>59</v>
+      </c>
+      <c r="V21">
+        <v>417138</v>
+      </c>
+      <c r="W21">
+        <v>417138</v>
+      </c>
+      <c r="X21">
+        <v>56714.8780934592</v>
+      </c>
+      <c r="Y21">
+        <v>113429.75618691801</v>
+      </c>
+      <c r="Z21">
+        <v>-1687.40184965618</v>
+      </c>
+      <c r="AA21">
+        <v>-1002808.09096253</v>
+      </c>
+      <c r="AB21">
+        <v>254.776716327858</v>
+      </c>
+      <c r="AC21">
+        <v>94.417283829464196</v>
+      </c>
+      <c r="AD21">
+        <v>1.63419308470433</v>
+      </c>
+      <c r="AE21">
+        <v>1.63419308470433</v>
+      </c>
+      <c r="AF21">
+        <v>1.31122650022987</v>
+      </c>
+      <c r="AG21">
+        <v>1.35681345389344</v>
+      </c>
+      <c r="AH21">
+        <v>1.5545760126919099</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="14" t="str">
+        <f>T22</f>
         <v>[95,100)</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C22" s="15">
         <v>418.13799999999998</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D22" s="15">
         <f t="shared" si="27"/>
         <v>109.06399999999999</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E22" s="25">
         <f t="shared" si="28"/>
         <v>14.8285494593756</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F22" s="26">
         <f t="shared" si="29"/>
         <v>1.65832522414388</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G22" s="15">
         <f t="shared" si="30"/>
         <v>29.657098918751302</v>
       </c>
-      <c r="H21" s="19">
+      <c r="H22" s="26">
         <f t="shared" si="31"/>
         <v>1.65832522414388</v>
       </c>
-      <c r="I21" s="17">
+      <c r="I22" s="15">
         <f t="shared" si="32"/>
         <v>277.23480019250798</v>
       </c>
-      <c r="J21" s="19">
+      <c r="J22" s="26">
         <f t="shared" si="33"/>
         <v>1.31572395022829</v>
       </c>
-      <c r="K21" s="17">
+      <c r="K22" s="15">
         <f t="shared" si="34"/>
         <v>40.5672077956918</v>
       </c>
-      <c r="L21" s="19">
+      <c r="L22" s="26">
         <f t="shared" si="35"/>
         <v>1.3633206697048801</v>
       </c>
-      <c r="M21" s="20">
+      <c r="M22" s="27">
         <f t="shared" si="36"/>
         <v>0.16826237552079701</v>
       </c>
-      <c r="N21" s="19">
+      <c r="N22" s="26">
         <f t="shared" si="37"/>
         <v>1.5673677035192299</v>
       </c>
-      <c r="O21" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$16:K21)) * 20 + (SUM($M$3:$M$5) + SUM($M$16:M21)) * 1000) /(SUM($G$3:$G$5) + SUM($G$16:G21))</f>
+      <c r="O22" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$17:K22)) * 20 + (SUM($M$4:$M$6) + SUM($M$17:M22)) * 1000) /(SUM($G$4:$G$6) + SUM($G$17:G22))</f>
         <v>93.523984986670172</v>
       </c>
-      <c r="P21" s="20">
+      <c r="P22" s="27">
         <f t="shared" si="39"/>
         <v>33.03109768485335</v>
       </c>
-      <c r="Q21" s="18">
+      <c r="Q22" s="25">
         <f t="shared" si="38"/>
         <v>53.487330771890328</v>
       </c>
-      <c r="S21" t="s">
+      <c r="S22" t="s">
         <v>55</v>
       </c>
-      <c r="T21" t="s">
+      <c r="T22" t="s">
         <v>28</v>
       </c>
-      <c r="U21" t="s">
+      <c r="U22" t="s">
         <v>59</v>
       </c>
-      <c r="V21">
+      <c r="V22">
         <v>109064</v>
       </c>
-      <c r="W21">
+      <c r="W22">
         <v>109064</v>
       </c>
-      <c r="X21">
+      <c r="X22">
         <v>14828.549459375599</v>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <v>29657.098918751301</v>
       </c>
-      <c r="Z21">
+      <c r="Z22">
         <v>-277.23480019250798</v>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <v>-168262.37552079701</v>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <v>40.5672077956918</v>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <v>93.523984986670101</v>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <v>1.65832522414388</v>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <v>1.65832522414388</v>
       </c>
-      <c r="AF21">
+      <c r="AF22">
         <v>1.31572395022829</v>
       </c>
-      <c r="AG21">
+      <c r="AG22">
         <v>1.3633206697048801</v>
       </c>
-      <c r="AH21">
+      <c r="AH22">
         <v>1.5673677035192299</v>
       </c>
-      <c r="AI21" t="s">
+      <c r="AI22" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="17">
-        <f>SUM(G16:G17)</f>
+    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="15">
+        <f>SUM(G17:G18)</f>
         <v>410.19625859714995</v>
       </c>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="20"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="14"/>
-    </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="18"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="27"/>
+      <c r="P23" s="14"/>
+      <c r="Q23" s="14"/>
     </row>
     <row r="24" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" s="22" t="str">
-        <f>T24</f>
-        <v>[80,85)</v>
-      </c>
-      <c r="C24" s="23">
-        <f>V24/1000</f>
-        <v>1508.4970000000001</v>
-      </c>
-      <c r="D24" s="17">
-        <f>W24/1000</f>
-        <v>1076.1643642254198</v>
-      </c>
-      <c r="E24" s="18">
-        <f t="shared" ref="E24:E29" si="40">X24 / 1000</f>
-        <v>256.73672542993097</v>
-      </c>
-      <c r="F24" s="19">
-        <f t="shared" ref="F24:F29" si="41">AD24</f>
-        <v>1.4178160833803599</v>
-      </c>
-      <c r="G24" s="17">
-        <f t="shared" ref="G24:G29" si="42">Y24 / 1000</f>
-        <v>256.73672542993097</v>
-      </c>
-      <c r="H24" s="19">
-        <f t="shared" ref="H24:H29" si="43">AE24</f>
-        <v>1.2089080416901801</v>
-      </c>
-      <c r="I24" s="17">
-        <f t="shared" ref="I24:I29" si="44">-Z24</f>
-        <v>12253.3163549091</v>
-      </c>
-      <c r="J24" s="19">
-        <f t="shared" ref="J24:J29" si="45">AF24</f>
-        <v>1.1987797981452399</v>
-      </c>
-      <c r="K24" s="17">
-        <f t="shared" ref="K24:K29" si="46">AB24</f>
-        <v>1220.2889671560499</v>
-      </c>
-      <c r="L24" s="19">
-        <f t="shared" ref="L24:L29" si="47">AG24</f>
-        <v>1.1957414397754</v>
-      </c>
-      <c r="M24" s="20">
-        <f t="shared" ref="M24:M29" si="48">-AA24/1000000</f>
-        <v>3.6361200818484201</v>
-      </c>
-      <c r="N24" s="19">
-        <f t="shared" ref="N24:N29" si="49">AH24</f>
-        <v>1.2764261692733001</v>
-      </c>
-      <c r="O24" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$24:K24)) * 20 + (SUM($M$3:$M$5) + SUM($M$24:M24)) * 1000) /(SUM($G$3:$G$5) + SUM($G$24:G24))</f>
-        <v>111.65216135811444</v>
-      </c>
-      <c r="P24" s="20">
-        <f>(K24 * 20 + M24 * 1000) /G24</f>
-        <v>109.22434014070443</v>
-      </c>
-      <c r="Q24" s="18">
-        <f t="shared" ref="Q24:Q29" si="50">E24/I24*1000</f>
-        <v>20.952427734151609</v>
-      </c>
-      <c r="S24" t="s">
-        <v>51</v>
-      </c>
-      <c r="T24" t="s">
-        <v>3</v>
-      </c>
-      <c r="U24" t="s">
-        <v>56</v>
-      </c>
-      <c r="V24">
-        <v>1508497</v>
-      </c>
-      <c r="W24">
-        <v>1076164.3642254199</v>
-      </c>
-      <c r="X24">
-        <v>256736.72542993099</v>
-      </c>
-      <c r="Y24">
-        <v>256736.72542993099</v>
-      </c>
-      <c r="Z24">
-        <v>-12253.3163549091</v>
-      </c>
-      <c r="AA24">
-        <v>-3636120.0818484202</v>
-      </c>
-      <c r="AB24">
-        <v>1220.2889671560499</v>
-      </c>
-      <c r="AC24">
-        <v>111.652161358114</v>
-      </c>
-      <c r="AD24">
-        <v>1.4178160833803599</v>
-      </c>
-      <c r="AE24">
-        <v>1.2089080416901801</v>
-      </c>
-      <c r="AF24">
-        <v>1.1987797981452399</v>
-      </c>
-      <c r="AG24">
-        <v>1.1957414397754</v>
-      </c>
-      <c r="AH24">
-        <v>1.2764261692733001</v>
-      </c>
-      <c r="AI24" t="s">
-        <v>63</v>
-      </c>
+      <c r="A24" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+      <c r="N24" s="31"/>
+      <c r="O24" s="31"/>
+      <c r="P24" s="27"/>
+      <c r="Q24" s="25"/>
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="20" t="str">
+        <f>T25</f>
+        <v>[80,85)</v>
+      </c>
+      <c r="C25" s="21">
+        <f>V25/1000</f>
+        <v>1508.4970000000001</v>
+      </c>
+      <c r="D25" s="15">
+        <f>W25/1000</f>
+        <v>1076.1643642254198</v>
+      </c>
+      <c r="E25" s="25">
+        <f t="shared" ref="E25:E30" si="40">X25 / 1000</f>
+        <v>256.73672542993097</v>
+      </c>
+      <c r="F25" s="26">
+        <f t="shared" ref="F25:F30" si="41">AD25</f>
+        <v>1.4178160833803599</v>
+      </c>
+      <c r="G25" s="15">
+        <f t="shared" ref="G25:G30" si="42">Y25 / 1000</f>
+        <v>256.73672542993097</v>
+      </c>
+      <c r="H25" s="26">
+        <f t="shared" ref="H25:H30" si="43">AE25</f>
+        <v>1.2089080416901801</v>
+      </c>
+      <c r="I25" s="15">
+        <f t="shared" ref="I25:I30" si="44">-Z25</f>
+        <v>12253.3163549091</v>
+      </c>
+      <c r="J25" s="26">
+        <f t="shared" ref="J25:J30" si="45">AF25</f>
+        <v>1.1987797981452399</v>
+      </c>
+      <c r="K25" s="15">
+        <f t="shared" ref="K25:K30" si="46">AB25</f>
+        <v>1220.2889671560499</v>
+      </c>
+      <c r="L25" s="26">
+        <f t="shared" ref="L25:L30" si="47">AG25</f>
+        <v>1.1957414397754</v>
+      </c>
+      <c r="M25" s="27">
+        <f t="shared" ref="M25:M30" si="48">-AA25/1000000</f>
+        <v>3.6361200818484201</v>
+      </c>
+      <c r="N25" s="26">
+        <f t="shared" ref="N25:N30" si="49">AH25</f>
+        <v>1.2764261692733001</v>
+      </c>
+      <c r="O25" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$25:K25)) * 20 + (SUM($M$4:$M$6) + SUM($M$25:M25)) * 1000) /(SUM($G$4:$G$6) + SUM($G$25:G25))</f>
+        <v>111.65216135811444</v>
+      </c>
+      <c r="P25" s="27">
+        <f>(K25 * 20 + M25 * 1000) /G25</f>
+        <v>109.22434014070443</v>
+      </c>
+      <c r="Q25" s="25">
+        <f t="shared" ref="Q25:Q30" si="50">E25/I25*1000</f>
+        <v>20.952427734151609</v>
+      </c>
+      <c r="S25" t="s">
+        <v>51</v>
+      </c>
+      <c r="T25" t="s">
+        <v>3</v>
+      </c>
+      <c r="U25" t="s">
+        <v>56</v>
+      </c>
+      <c r="V25">
+        <v>1508497</v>
+      </c>
+      <c r="W25">
+        <v>1076164.3642254199</v>
+      </c>
+      <c r="X25">
+        <v>256736.72542993099</v>
+      </c>
+      <c r="Y25">
+        <v>256736.72542993099</v>
+      </c>
+      <c r="Z25">
+        <v>-12253.3163549091</v>
+      </c>
+      <c r="AA25">
+        <v>-3636120.0818484202</v>
+      </c>
+      <c r="AB25">
+        <v>1220.2889671560499</v>
+      </c>
+      <c r="AC25">
+        <v>111.652161358114</v>
+      </c>
+      <c r="AD25">
+        <v>1.4178160833803599</v>
+      </c>
+      <c r="AE25">
+        <v>1.2089080416901801</v>
+      </c>
+      <c r="AF25">
+        <v>1.1987797981452399</v>
+      </c>
+      <c r="AG25">
+        <v>1.1957414397754</v>
+      </c>
+      <c r="AH25">
+        <v>1.2764261692733001</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="17">
-        <f t="shared" ref="D25:D29" si="51">W25/1000</f>
+      <c r="B26" s="20"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="15">
+        <f t="shared" ref="D26:D30" si="51">W26/1000</f>
         <v>432.33263577457899</v>
       </c>
-      <c r="E25" s="18">
+      <c r="E26" s="25">
         <f t="shared" si="40"/>
         <v>76.633207778455898</v>
       </c>
-      <c r="F25" s="19">
+      <c r="F26" s="26">
         <f t="shared" si="41"/>
         <v>1.54252978251027</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G26" s="15">
         <f t="shared" si="42"/>
         <v>76.633207778455898</v>
       </c>
-      <c r="H25" s="19">
+      <c r="H26" s="26">
         <f t="shared" si="43"/>
         <v>1.2712648912551301</v>
       </c>
-      <c r="I25" s="17">
+      <c r="I26" s="15">
         <f t="shared" si="44"/>
         <v>4000.1614705817601</v>
       </c>
-      <c r="J25" s="19">
+      <c r="J26" s="26">
         <f t="shared" si="45"/>
         <v>1.26367253955823</v>
       </c>
-      <c r="K25" s="17">
+      <c r="K26" s="15">
         <f t="shared" si="46"/>
         <v>524.266627907724</v>
       </c>
-      <c r="L25" s="19">
+      <c r="L26" s="26">
         <f t="shared" si="47"/>
         <v>1.2798368526938899</v>
       </c>
-      <c r="M25" s="20">
+      <c r="M26" s="27">
         <f t="shared" si="48"/>
         <v>1.5644777091581601</v>
       </c>
-      <c r="N25" s="19">
+      <c r="N26" s="26">
         <f t="shared" si="49"/>
         <v>1.3953613447684501</v>
       </c>
-      <c r="O25" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$24:K25)) * 20 + (SUM($M$3:$M$5) + SUM($M$24:M25)) * 1000) /(SUM($G$3:$G$5) + SUM($G$24:G25))</f>
+      <c r="O26" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$25:K26)) * 20 + (SUM($M$4:$M$6) + SUM($M$25:M26)) * 1000) /(SUM($G$4:$G$6) + SUM($G$25:G26))</f>
         <v>113.8882946933541</v>
       </c>
-      <c r="P25" s="20">
-        <f t="shared" ref="P25:P29" si="52">(K25 * 20 + M25 * 1000) /G25</f>
+      <c r="P26" s="27">
+        <f t="shared" ref="P26:P30" si="52">(K26 * 20 + M26 * 1000) /G26</f>
         <v>157.24006102091207</v>
       </c>
-      <c r="Q25" s="18">
+      <c r="Q26" s="25">
         <f t="shared" si="50"/>
         <v>19.157528600291929</v>
       </c>
-      <c r="S25" t="s">
+      <c r="S26" t="s">
         <v>52</v>
       </c>
-      <c r="T25" t="s">
+      <c r="T26" t="s">
         <v>3</v>
       </c>
-      <c r="U25" t="s">
+      <c r="U26" t="s">
         <v>57</v>
       </c>
-      <c r="V25">
+      <c r="V26">
         <v>1508497</v>
       </c>
-      <c r="W25">
+      <c r="W26">
         <v>432332.63577457902</v>
       </c>
-      <c r="X25">
+      <c r="X26">
         <v>76633.207778455893</v>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <v>76633.207778455893</v>
       </c>
-      <c r="Z25">
+      <c r="Z26">
         <v>-4000.1614705817601</v>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <v>-1564477.70915816</v>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <v>524.266627907724</v>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <v>113.888294693354</v>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <v>1.54252978251027</v>
       </c>
-      <c r="AE25">
+      <c r="AE26">
         <v>1.2712648912551301</v>
       </c>
-      <c r="AF25">
+      <c r="AF26">
         <v>1.26367253955823</v>
       </c>
-      <c r="AG25">
+      <c r="AG26">
         <v>1.2798368526938899</v>
       </c>
-      <c r="AH25">
+      <c r="AH26">
         <v>1.3953613447684501</v>
       </c>
-      <c r="AI25" t="s">
+      <c r="AI26" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B26" s="22" t="str">
-        <f>T26</f>
+      <c r="B27" s="20" t="str">
+        <f>T27</f>
         <v>[85,90)</v>
       </c>
-      <c r="C26" s="23">
-        <f>V26/1000</f>
+      <c r="C27" s="21">
+        <f>V27/1000</f>
         <v>940.56899999999996</v>
       </c>
-      <c r="D26" s="17">
+      <c r="D27" s="15">
         <f t="shared" si="51"/>
         <v>344.866124798366</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E27" s="25">
         <f t="shared" si="40"/>
         <v>46.888656095831699</v>
       </c>
-      <c r="F26" s="19">
+      <c r="F27" s="26">
         <f t="shared" si="41"/>
         <v>1.6188368812010501</v>
       </c>
-      <c r="G26" s="17">
+      <c r="G27" s="15">
         <f t="shared" si="42"/>
         <v>46.888656095831699</v>
       </c>
-      <c r="H26" s="19">
+      <c r="H27" s="26">
         <f t="shared" si="43"/>
         <v>1.30941844060052</v>
       </c>
-      <c r="I26" s="17">
+      <c r="I27" s="15">
         <f t="shared" si="44"/>
         <v>2013.8918608971601</v>
       </c>
-      <c r="J26" s="19">
+      <c r="J27" s="26">
         <f t="shared" si="45"/>
         <v>1.2963429616709401</v>
       </c>
-      <c r="K26" s="17">
+      <c r="K27" s="15">
         <f t="shared" si="46"/>
         <v>172.28852391461299</v>
       </c>
-      <c r="L26" s="19">
+      <c r="L27" s="26">
         <f t="shared" si="47"/>
         <v>1.3074729328646499</v>
       </c>
-      <c r="M26" s="20">
+      <c r="M27" s="27">
         <f t="shared" si="48"/>
         <v>0.59842974890966394</v>
       </c>
-      <c r="N26" s="19">
+      <c r="N27" s="26">
         <f t="shared" si="49"/>
         <v>1.44085534368671</v>
       </c>
-      <c r="O26" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$24:K26)) * 20 + (SUM($M$3:$M$5) + SUM($M$24:M26)) * 1000) /(SUM($G$3:$G$5) + SUM($G$24:G26))</f>
+      <c r="O27" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$25:K27)) * 20 + (SUM($M$4:$M$6) + SUM($M$25:M27)) * 1000) /(SUM($G$4:$G$6) + SUM($G$25:G27))</f>
         <v>113.08300941446858</v>
       </c>
-      <c r="P26" s="20">
+      <c r="P27" s="27">
         <f t="shared" si="52"/>
         <v>86.251143964039628</v>
       </c>
-      <c r="Q26" s="18">
+      <c r="Q27" s="25">
         <f t="shared" si="50"/>
         <v>23.282608667450233</v>
       </c>
-      <c r="S26" t="s">
+      <c r="S27" t="s">
         <v>53</v>
-      </c>
-      <c r="T26" t="s">
-        <v>4</v>
-      </c>
-      <c r="U26" t="s">
-        <v>56</v>
-      </c>
-      <c r="V26">
-        <v>940569</v>
-      </c>
-      <c r="W26">
-        <v>344866.12479836599</v>
-      </c>
-      <c r="X26">
-        <v>46888.656095831699</v>
-      </c>
-      <c r="Y26">
-        <v>46888.656095831699</v>
-      </c>
-      <c r="Z26">
-        <v>-2013.8918608971601</v>
-      </c>
-      <c r="AA26">
-        <v>-598429.74890966399</v>
-      </c>
-      <c r="AB26">
-        <v>172.28852391461299</v>
-      </c>
-      <c r="AC26">
-        <v>113.08300941446799</v>
-      </c>
-      <c r="AD26">
-        <v>1.6188368812010501</v>
-      </c>
-      <c r="AE26">
-        <v>1.30941844060052</v>
-      </c>
-      <c r="AF26">
-        <v>1.2963429616709401</v>
-      </c>
-      <c r="AG26">
-        <v>1.3074729328646499</v>
-      </c>
-      <c r="AH26">
-        <v>1.44085534368671</v>
-      </c>
-      <c r="AI26" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27" s="22"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="17">
-        <f t="shared" si="51"/>
-        <v>595.70287520163299</v>
-      </c>
-      <c r="E27" s="18">
-        <f t="shared" si="40"/>
-        <v>80.992899105293191</v>
-      </c>
-      <c r="F27" s="19">
-        <f t="shared" si="41"/>
-        <v>1.7506455884638199</v>
-      </c>
-      <c r="G27" s="17">
-        <f t="shared" si="42"/>
-        <v>80.992899105293191</v>
-      </c>
-      <c r="H27" s="19">
-        <f t="shared" si="43"/>
-        <v>1.37532279423191</v>
-      </c>
-      <c r="I27" s="17">
-        <f t="shared" si="44"/>
-        <v>2991.2900760042098</v>
-      </c>
-      <c r="J27" s="19">
-        <f t="shared" si="45"/>
-        <v>1.3448692561270399</v>
-      </c>
-      <c r="K27" s="17">
-        <f t="shared" si="46"/>
-        <v>429.17134849906301</v>
-      </c>
-      <c r="L27" s="19">
-        <f t="shared" si="47"/>
-        <v>1.3763145104963399</v>
-      </c>
-      <c r="M27" s="20">
-        <f t="shared" si="48"/>
-        <v>1.50351979253798</v>
-      </c>
-      <c r="N27" s="19">
-        <f t="shared" si="49"/>
-        <v>1.5551563588684201</v>
-      </c>
-      <c r="O27" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$24:K27)) * 20 + (SUM($M$3:$M$5) + SUM($M$24:M27)) * 1000) /(SUM($G$3:$G$5) + SUM($G$24:G27))</f>
-        <v>113.63207302141855</v>
-      </c>
-      <c r="P27" s="20">
-        <f t="shared" si="52"/>
-        <v>124.54112488807085</v>
-      </c>
-      <c r="Q27" s="18">
-        <f t="shared" si="50"/>
-        <v>27.076243710033022</v>
-      </c>
-      <c r="S27" t="s">
-        <v>54</v>
       </c>
       <c r="T27" t="s">
         <v>4</v>
       </c>
       <c r="U27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V27">
         <v>940569</v>
       </c>
       <c r="W27">
-        <v>595702.87520163297</v>
+        <v>344866.12479836599</v>
       </c>
       <c r="X27">
-        <v>80992.899105293196</v>
+        <v>46888.656095831699</v>
       </c>
       <c r="Y27">
-        <v>80992.899105293196</v>
+        <v>46888.656095831699</v>
       </c>
       <c r="Z27">
-        <v>-2991.2900760042098</v>
+        <v>-2013.8918608971601</v>
       </c>
       <c r="AA27">
-        <v>-1503519.79253798</v>
+        <v>-598429.74890966399</v>
       </c>
       <c r="AB27">
-        <v>429.17134849906301</v>
+        <v>172.28852391461299</v>
       </c>
       <c r="AC27">
-        <v>113.63207302141799</v>
+        <v>113.08300941446799</v>
       </c>
       <c r="AD27">
-        <v>1.7506455884638199</v>
+        <v>1.6188368812010501</v>
       </c>
       <c r="AE27">
-        <v>1.37532279423191</v>
+        <v>1.30941844060052</v>
       </c>
       <c r="AF27">
-        <v>1.3448692561270399</v>
+        <v>1.2963429616709401</v>
       </c>
       <c r="AG27">
-        <v>1.3763145104963399</v>
+        <v>1.3074729328646499</v>
       </c>
       <c r="AH27">
-        <v>1.5551563588684201</v>
+        <v>1.44085534368671</v>
       </c>
       <c r="AI27" t="s">
         <v>63</v>
@@ -3212,117 +3200,111 @@
       <c r="A28" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="15" t="str">
-        <f>T28</f>
-        <v>[90,95)</v>
-      </c>
-      <c r="C28" s="16">
-        <f>V28/1000</f>
-        <v>417.13799999999998</v>
-      </c>
-      <c r="D28" s="17">
+      <c r="B28" s="20"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="15">
         <f t="shared" si="51"/>
-        <v>417.13799999999998</v>
-      </c>
-      <c r="E28" s="18">
+        <v>595.70287520163299</v>
+      </c>
+      <c r="E28" s="25">
         <f t="shared" si="40"/>
-        <v>56.714878093459198</v>
-      </c>
-      <c r="F28" s="19">
+        <v>80.992899105293191</v>
+      </c>
+      <c r="F28" s="26">
         <f t="shared" si="41"/>
-        <v>1.8429439855658301</v>
-      </c>
-      <c r="G28" s="17">
+        <v>1.7506455884638199</v>
+      </c>
+      <c r="G28" s="15">
         <f t="shared" si="42"/>
-        <v>56.714878093459198</v>
-      </c>
-      <c r="H28" s="19">
+        <v>80.992899105293191</v>
+      </c>
+      <c r="H28" s="26">
         <f t="shared" si="43"/>
-        <v>1.42147199278291</v>
-      </c>
-      <c r="I28" s="17">
+        <v>1.37532279423191</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="44"/>
-        <v>1477.3691476014601</v>
-      </c>
-      <c r="J28" s="19">
+        <v>2991.2900760042098</v>
+      </c>
+      <c r="J28" s="26">
         <f t="shared" si="45"/>
-        <v>1.3688359221658699</v>
-      </c>
-      <c r="K28" s="17">
+        <v>1.3448692561270399</v>
+      </c>
+      <c r="K28" s="15">
         <f t="shared" si="46"/>
-        <v>222.88904099605199</v>
-      </c>
-      <c r="L28" s="19">
+        <v>429.17134849906301</v>
+      </c>
+      <c r="L28" s="26">
         <f t="shared" si="47"/>
-        <v>1.4120672075779199</v>
-      </c>
-      <c r="M28" s="20">
+        <v>1.3763145104963399</v>
+      </c>
+      <c r="M28" s="27">
         <f t="shared" si="48"/>
-        <v>0.87716270430148302</v>
-      </c>
-      <c r="N28" s="19">
+        <v>1.50351979253798</v>
+      </c>
+      <c r="N28" s="26">
         <f t="shared" si="49"/>
-        <v>1.62184027488921</v>
-      </c>
-      <c r="O28" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$24:K28)) * 20 + (SUM($M$3:$M$5) + SUM($M$24:M28)) * 1000) /(SUM($G$3:$G$5) + SUM($G$24:G28))</f>
-        <v>112.99684620904588</v>
-      </c>
-      <c r="P28" s="20">
+        <v>1.5551563588684201</v>
+      </c>
+      <c r="O28" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$25:K28)) * 20 + (SUM($M$4:$M$6) + SUM($M$25:M28)) * 1000) /(SUM($G$4:$G$6) + SUM($G$25:G28))</f>
+        <v>113.63207302141855</v>
+      </c>
+      <c r="P28" s="27">
         <f t="shared" si="52"/>
-        <v>94.066031763855449</v>
-      </c>
-      <c r="Q28" s="18">
+        <v>124.54112488807085</v>
+      </c>
+      <c r="Q28" s="25">
         <f t="shared" si="50"/>
-        <v>38.389104162312442</v>
+        <v>27.076243710033022</v>
       </c>
       <c r="S28" t="s">
         <v>54</v>
       </c>
       <c r="T28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U28" t="s">
         <v>57</v>
       </c>
       <c r="V28">
-        <v>417138</v>
+        <v>940569</v>
       </c>
       <c r="W28">
-        <v>417138</v>
+        <v>595702.87520163297</v>
       </c>
       <c r="X28">
-        <v>56714.8780934592</v>
+        <v>80992.899105293196</v>
       </c>
       <c r="Y28">
-        <v>56714.8780934592</v>
+        <v>80992.899105293196</v>
       </c>
       <c r="Z28">
-        <v>-1477.3691476014601</v>
+        <v>-2991.2900760042098</v>
       </c>
       <c r="AA28">
-        <v>-877162.704301483</v>
+        <v>-1503519.79253798</v>
       </c>
       <c r="AB28">
-        <v>222.88904099605199</v>
+        <v>429.17134849906301</v>
       </c>
       <c r="AC28">
-        <v>112.996846209046</v>
+        <v>113.63207302141799</v>
       </c>
       <c r="AD28">
-        <v>1.8429439855658301</v>
+        <v>1.7506455884638199</v>
       </c>
       <c r="AE28">
-        <v>1.42147199278291</v>
+        <v>1.37532279423191</v>
       </c>
       <c r="AF28">
-        <v>1.3688359221658699</v>
+        <v>1.3448692561270399</v>
       </c>
       <c r="AG28">
-        <v>1.4120672075779199</v>
+        <v>1.3763145104963399</v>
       </c>
       <c r="AH28">
-        <v>1.62184027488921</v>
+        <v>1.5551563588684201</v>
       </c>
       <c r="AI28" t="s">
         <v>63</v>
@@ -3332,625 +3314,631 @@
       <c r="A29" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="15" t="str">
+      <c r="B29" s="14" t="str">
         <f>T29</f>
+        <v>[90,95)</v>
+      </c>
+      <c r="C29" s="15">
+        <f>V29/1000</f>
+        <v>417.13799999999998</v>
+      </c>
+      <c r="D29" s="15">
+        <f t="shared" si="51"/>
+        <v>417.13799999999998</v>
+      </c>
+      <c r="E29" s="25">
+        <f t="shared" si="40"/>
+        <v>56.714878093459198</v>
+      </c>
+      <c r="F29" s="26">
+        <f t="shared" si="41"/>
+        <v>1.8429439855658301</v>
+      </c>
+      <c r="G29" s="15">
+        <f t="shared" si="42"/>
+        <v>56.714878093459198</v>
+      </c>
+      <c r="H29" s="26">
+        <f t="shared" si="43"/>
+        <v>1.42147199278291</v>
+      </c>
+      <c r="I29" s="15">
+        <f t="shared" si="44"/>
+        <v>1477.3691476014601</v>
+      </c>
+      <c r="J29" s="26">
+        <f t="shared" si="45"/>
+        <v>1.3688359221658699</v>
+      </c>
+      <c r="K29" s="15">
+        <f t="shared" si="46"/>
+        <v>222.88904099605199</v>
+      </c>
+      <c r="L29" s="26">
+        <f t="shared" si="47"/>
+        <v>1.4120672075779199</v>
+      </c>
+      <c r="M29" s="27">
+        <f t="shared" si="48"/>
+        <v>0.87716270430148302</v>
+      </c>
+      <c r="N29" s="26">
+        <f t="shared" si="49"/>
+        <v>1.62184027488921</v>
+      </c>
+      <c r="O29" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$25:K29)) * 20 + (SUM($M$4:$M$6) + SUM($M$25:M29)) * 1000) /(SUM($G$4:$G$6) + SUM($G$25:G29))</f>
+        <v>112.99684620904588</v>
+      </c>
+      <c r="P29" s="27">
+        <f t="shared" si="52"/>
+        <v>94.066031763855449</v>
+      </c>
+      <c r="Q29" s="25">
+        <f t="shared" si="50"/>
+        <v>38.389104162312442</v>
+      </c>
+      <c r="S29" t="s">
+        <v>54</v>
+      </c>
+      <c r="T29" t="s">
+        <v>5</v>
+      </c>
+      <c r="U29" t="s">
+        <v>57</v>
+      </c>
+      <c r="V29">
+        <v>417138</v>
+      </c>
+      <c r="W29">
+        <v>417138</v>
+      </c>
+      <c r="X29">
+        <v>56714.8780934592</v>
+      </c>
+      <c r="Y29">
+        <v>56714.8780934592</v>
+      </c>
+      <c r="Z29">
+        <v>-1477.3691476014601</v>
+      </c>
+      <c r="AA29">
+        <v>-877162.704301483</v>
+      </c>
+      <c r="AB29">
+        <v>222.88904099605199</v>
+      </c>
+      <c r="AC29">
+        <v>112.996846209046</v>
+      </c>
+      <c r="AD29">
+        <v>1.8429439855658301</v>
+      </c>
+      <c r="AE29">
+        <v>1.42147199278291</v>
+      </c>
+      <c r="AF29">
+        <v>1.3688359221658699</v>
+      </c>
+      <c r="AG29">
+        <v>1.4120672075779199</v>
+      </c>
+      <c r="AH29">
+        <v>1.62184027488921</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="14" t="str">
+        <f>T30</f>
         <v>[95,100)</v>
       </c>
-      <c r="C29" s="16">
-        <f>V29/1000</f>
+      <c r="C30" s="15">
+        <f>V30/1000</f>
         <v>109.06399999999999</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D30" s="15">
         <f t="shared" si="51"/>
         <v>109.06399999999999</v>
       </c>
-      <c r="E29" s="18">
+      <c r="E30" s="25">
         <f t="shared" si="40"/>
         <v>14.8285494593756</v>
       </c>
-      <c r="F29" s="19">
+      <c r="F30" s="26">
         <f t="shared" si="41"/>
         <v>1.86707612500538</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G30" s="15">
         <f t="shared" si="42"/>
         <v>14.8285494593756</v>
       </c>
-      <c r="H29" s="19">
+      <c r="H30" s="26">
         <f t="shared" si="43"/>
         <v>1.4335380625026899</v>
       </c>
-      <c r="I29" s="17">
+      <c r="I30" s="15">
         <f t="shared" si="44"/>
         <v>242.50151599851301</v>
       </c>
-      <c r="J29" s="19">
+      <c r="J30" s="26">
         <f t="shared" si="45"/>
         <v>1.37276991040251</v>
       </c>
-      <c r="K29" s="17">
+      <c r="K30" s="15">
         <f t="shared" si="46"/>
         <v>35.483222543958902</v>
       </c>
-      <c r="L29" s="19">
+      <c r="L30" s="26">
         <f t="shared" si="47"/>
         <v>1.4177589226188301</v>
       </c>
-      <c r="M29" s="20">
+      <c r="M30" s="27">
         <f t="shared" si="48"/>
         <v>0.147012741783423</v>
       </c>
-      <c r="N29" s="19">
+      <c r="N30" s="26">
         <f t="shared" si="49"/>
         <v>1.6330165199336</v>
       </c>
-      <c r="O29" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$24:K29)) * 20 + (SUM($M$3:$M$5) + SUM($M$24:M29)) * 1000) /(SUM($G$3:$G$5) + SUM($G$24:G29))</f>
+      <c r="O30" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$25:K30)) * 20 + (SUM($M$4:$M$6) + SUM($M$25:M30)) * 1000) /(SUM($G$4:$G$6) + SUM($G$25:G30))</f>
         <v>112.53202072250498</v>
       </c>
-      <c r="P29" s="20">
+      <c r="P30" s="27">
         <f t="shared" si="52"/>
         <v>57.772150607823107</v>
       </c>
-      <c r="Q29" s="18">
+      <c r="Q30" s="25">
         <f t="shared" si="50"/>
         <v>61.148275293530645</v>
       </c>
-      <c r="S29" t="s">
+      <c r="S30" t="s">
         <v>55</v>
       </c>
-      <c r="T29" t="s">
+      <c r="T30" t="s">
         <v>28</v>
       </c>
-      <c r="U29" t="s">
+      <c r="U30" t="s">
         <v>57</v>
       </c>
-      <c r="V29">
+      <c r="V30">
         <v>109064</v>
       </c>
-      <c r="W29">
+      <c r="W30">
         <v>109064</v>
       </c>
-      <c r="X29">
+      <c r="X30">
         <v>14828.549459375599</v>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <v>14828.549459375599</v>
       </c>
-      <c r="Z29">
+      <c r="Z30">
         <v>-242.50151599851301</v>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <v>-147012.741783423</v>
       </c>
-      <c r="AB29">
+      <c r="AB30">
         <v>35.483222543958902</v>
       </c>
-      <c r="AC29">
+      <c r="AC30">
         <v>112.532020722505</v>
       </c>
-      <c r="AD29">
+      <c r="AD30">
         <v>1.86707612500538</v>
       </c>
-      <c r="AE29">
+      <c r="AE30">
         <v>1.4335380625026899</v>
       </c>
-      <c r="AF29">
+      <c r="AF30">
         <v>1.37276991040251</v>
       </c>
-      <c r="AG29">
+      <c r="AG30">
         <v>1.4177589226188301</v>
       </c>
-      <c r="AH29">
+      <c r="AH30">
         <v>1.6330165199336</v>
       </c>
-      <c r="AI29" t="s">
+      <c r="AI30" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="20"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="20"/>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="14"/>
-    </row>
     <row r="31" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A31" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="B31" s="24"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
-      <c r="M31" s="24"/>
-      <c r="N31" s="24"/>
-      <c r="O31" s="24"/>
-      <c r="P31" s="20"/>
-      <c r="Q31" s="18"/>
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="27"/>
+      <c r="N31" s="26"/>
+      <c r="O31" s="27"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="14"/>
     </row>
     <row r="32" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B32" s="22" t="str">
-        <f>T32</f>
-        <v>[80,85)</v>
-      </c>
-      <c r="C32" s="23">
-        <f>V32/1000</f>
-        <v>1508.4970000000001</v>
-      </c>
-      <c r="D32" s="17">
-        <f>W32/1000</f>
-        <v>1076.1643642254198</v>
-      </c>
-      <c r="E32" s="18">
-        <f t="shared" ref="E32:E37" si="53">X32 / 1000</f>
-        <v>256.73672542993097</v>
-      </c>
-      <c r="F32" s="19">
-        <f t="shared" ref="F32:F37" si="54">AD32</f>
-        <v>1.4178160833803599</v>
-      </c>
-      <c r="G32" s="17">
-        <f t="shared" ref="G32:G37" si="55">Y32 / 1000</f>
-        <v>513.47345085986194</v>
-      </c>
-      <c r="H32" s="19">
-        <f t="shared" ref="H32:H37" si="56">AE32</f>
-        <v>1.4178160833803599</v>
-      </c>
-      <c r="I32" s="17">
-        <f t="shared" ref="I32:I37" si="57">-Z32</f>
-        <v>14993.793511620101</v>
-      </c>
-      <c r="J32" s="19">
-        <f t="shared" ref="J32:J37" si="58">AF32</f>
-        <v>1.2432372723713501</v>
-      </c>
-      <c r="K32" s="17">
-        <f t="shared" ref="K32:K37" si="59">AB32</f>
-        <v>1498.5521129625399</v>
-      </c>
-      <c r="L32" s="19">
-        <f t="shared" ref="L32:L37" si="60">AG32</f>
-        <v>1.2403764649723701</v>
-      </c>
-      <c r="M32" s="20">
-        <f t="shared" ref="M32:M37" si="61">-AA32/1000000</f>
-        <v>4.4373989306821198</v>
-      </c>
-      <c r="N32" s="19">
-        <f t="shared" ref="N32:N37" si="62">AH32</f>
-        <v>1.3373412209539499</v>
-      </c>
-      <c r="O32" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$32:K32)) * 20 + (SUM($M$3:$M$5) + SUM($M$32:M32)) * 1000) /(SUM($G$3:$G$5) + SUM($G$32:G32))</f>
-        <v>98.854630261095551</v>
-      </c>
-      <c r="P32" s="20">
-        <f>(K32 * 20 + M32 * 1000) /G32</f>
-        <v>67.011139782032714</v>
-      </c>
-      <c r="Q32" s="18">
-        <f t="shared" ref="Q32:Q37" si="63">E32/I32*1000</f>
-        <v>17.122866553481717</v>
-      </c>
-      <c r="S32" t="s">
-        <v>51</v>
-      </c>
-      <c r="T32" t="s">
-        <v>3</v>
-      </c>
-      <c r="U32" t="s">
-        <v>58</v>
-      </c>
-      <c r="V32">
-        <v>1508497</v>
-      </c>
-      <c r="W32">
-        <v>1076164.3642254199</v>
-      </c>
-      <c r="X32">
-        <v>256736.72542993099</v>
-      </c>
-      <c r="Y32">
-        <v>513473.45085986197</v>
-      </c>
-      <c r="Z32">
-        <v>-14993.793511620101</v>
-      </c>
-      <c r="AA32">
-        <v>-4437398.9306821199</v>
-      </c>
-      <c r="AB32">
-        <v>1498.5521129625399</v>
-      </c>
-      <c r="AC32">
-        <v>98.854630261095593</v>
-      </c>
-      <c r="AD32">
-        <v>1.4178160833803599</v>
-      </c>
-      <c r="AE32">
-        <v>1.4178160833803599</v>
-      </c>
-      <c r="AF32">
-        <v>1.2432372723713501</v>
-      </c>
-      <c r="AG32">
-        <v>1.2403764649723701</v>
-      </c>
-      <c r="AH32">
-        <v>1.3373412209539499</v>
-      </c>
-      <c r="AI32" t="s">
-        <v>64</v>
-      </c>
+      <c r="A32" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="27"/>
+      <c r="Q32" s="25"/>
     </row>
     <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" s="20" t="str">
+        <f>T33</f>
+        <v>[80,85)</v>
+      </c>
+      <c r="C33" s="21">
+        <f>V33/1000</f>
+        <v>1508.4970000000001</v>
+      </c>
+      <c r="D33" s="15">
+        <f>W33/1000</f>
+        <v>1076.1643642254198</v>
+      </c>
+      <c r="E33" s="25">
+        <f t="shared" ref="E33:E38" si="53">X33 / 1000</f>
+        <v>256.73672542993097</v>
+      </c>
+      <c r="F33" s="26">
+        <f t="shared" ref="F33:F38" si="54">AD33</f>
+        <v>1.4178160833803599</v>
+      </c>
+      <c r="G33" s="15">
+        <f t="shared" ref="G33:G38" si="55">Y33 / 1000</f>
+        <v>513.47345085986194</v>
+      </c>
+      <c r="H33" s="26">
+        <f t="shared" ref="H33:H38" si="56">AE33</f>
+        <v>1.4178160833803599</v>
+      </c>
+      <c r="I33" s="15">
+        <f t="shared" ref="I33:I38" si="57">-Z33</f>
+        <v>14993.793511620101</v>
+      </c>
+      <c r="J33" s="26">
+        <f t="shared" ref="J33:J38" si="58">AF33</f>
+        <v>1.2432372723713501</v>
+      </c>
+      <c r="K33" s="15">
+        <f t="shared" ref="K33:K38" si="59">AB33</f>
+        <v>1498.5521129625399</v>
+      </c>
+      <c r="L33" s="26">
+        <f t="shared" ref="L33:L38" si="60">AG33</f>
+        <v>1.2403764649723701</v>
+      </c>
+      <c r="M33" s="27">
+        <f t="shared" ref="M33:M38" si="61">-AA33/1000000</f>
+        <v>4.4373989306821198</v>
+      </c>
+      <c r="N33" s="26">
+        <f t="shared" ref="N33:N38" si="62">AH33</f>
+        <v>1.3373412209539499</v>
+      </c>
+      <c r="O33" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$33:K33)) * 20 + (SUM($M$4:$M$6) + SUM($M$33:M33)) * 1000) /(SUM($G$4:$G$6) + SUM($G$33:G33))</f>
+        <v>98.854630261095551</v>
+      </c>
+      <c r="P33" s="27">
+        <f>(K33 * 20 + M33 * 1000) /G33</f>
+        <v>67.011139782032714</v>
+      </c>
+      <c r="Q33" s="25">
+        <f t="shared" ref="Q33:Q38" si="63">E33/I33*1000</f>
+        <v>17.122866553481717</v>
+      </c>
+      <c r="S33" t="s">
+        <v>51</v>
+      </c>
+      <c r="T33" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" t="s">
+        <v>58</v>
+      </c>
+      <c r="V33">
+        <v>1508497</v>
+      </c>
+      <c r="W33">
+        <v>1076164.3642254199</v>
+      </c>
+      <c r="X33">
+        <v>256736.72542993099</v>
+      </c>
+      <c r="Y33">
+        <v>513473.45085986197</v>
+      </c>
+      <c r="Z33">
+        <v>-14993.793511620101</v>
+      </c>
+      <c r="AA33">
+        <v>-4437398.9306821199</v>
+      </c>
+      <c r="AB33">
+        <v>1498.5521129625399</v>
+      </c>
+      <c r="AC33">
+        <v>98.854630261095593</v>
+      </c>
+      <c r="AD33">
+        <v>1.4178160833803599</v>
+      </c>
+      <c r="AE33">
+        <v>1.4178160833803599</v>
+      </c>
+      <c r="AF33">
+        <v>1.2432372723713501</v>
+      </c>
+      <c r="AG33">
+        <v>1.2403764649723701</v>
+      </c>
+      <c r="AH33">
+        <v>1.3373412209539499</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="22"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="17">
-        <f t="shared" ref="D33:D37" si="64">W33/1000</f>
+      <c r="B34" s="20"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="15">
+        <f t="shared" ref="D34:D38" si="64">W34/1000</f>
         <v>432.33263577457899</v>
       </c>
-      <c r="E33" s="18">
+      <c r="E34" s="25">
         <f t="shared" si="53"/>
         <v>76.633207778455898</v>
       </c>
-      <c r="F33" s="19">
+      <c r="F34" s="26">
         <f t="shared" si="54"/>
         <v>1.54252978251027</v>
       </c>
-      <c r="G33" s="17">
+      <c r="G34" s="15">
         <f t="shared" si="55"/>
         <v>153.266415556911</v>
       </c>
-      <c r="H33" s="19">
+      <c r="H34" s="26">
         <f t="shared" si="56"/>
         <v>1.54252978251027</v>
       </c>
-      <c r="I33" s="17">
+      <c r="I34" s="15">
         <f t="shared" si="57"/>
         <v>4579.8958977517204</v>
       </c>
-      <c r="J33" s="19">
+      <c r="J34" s="26">
         <f t="shared" si="58"/>
         <v>1.3175347732039699</v>
       </c>
-      <c r="K33" s="17">
+      <c r="K34" s="15">
         <f t="shared" si="59"/>
         <v>599.73654430174201</v>
       </c>
-      <c r="L33" s="19">
+      <c r="L34" s="26">
         <f t="shared" si="60"/>
         <v>1.3365776909337499</v>
       </c>
-      <c r="M33" s="20">
+      <c r="M34" s="27">
         <f t="shared" si="61"/>
         <v>1.7897514454472101</v>
       </c>
-      <c r="N33" s="19">
+      <c r="N34" s="26">
         <f t="shared" si="62"/>
         <v>1.4734022213829701</v>
       </c>
-      <c r="O33" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$32:K33)) * 20 + (SUM($M$3:$M$5) + SUM($M$32:M33)) * 1000) /(SUM($G$3:$G$5) + SUM($G$32:G33))</f>
+      <c r="O34" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$33:K34)) * 20 + (SUM($M$4:$M$6) + SUM($M$33:M34)) * 1000) /(SUM($G$4:$G$6) + SUM($G$33:G34))</f>
         <v>98.133723673196229</v>
       </c>
-      <c r="P33" s="20">
-        <f t="shared" ref="P33:P37" si="65">(K33 * 20 + M33 * 1000) /G33</f>
+      <c r="P34" s="27">
+        <f t="shared" ref="P34:P38" si="65">(K34 * 20 + M34 * 1000) /G34</f>
         <v>89.938048602458409</v>
       </c>
-      <c r="Q33" s="18">
+      <c r="Q34" s="25">
         <f t="shared" si="63"/>
         <v>16.732521762356058</v>
       </c>
-      <c r="S33" t="s">
+      <c r="S34" t="s">
         <v>52</v>
       </c>
-      <c r="T33" t="s">
+      <c r="T34" t="s">
         <v>3</v>
       </c>
-      <c r="U33" t="s">
+      <c r="U34" t="s">
         <v>59</v>
       </c>
-      <c r="V33">
+      <c r="V34">
         <v>1508497</v>
       </c>
-      <c r="W33">
+      <c r="W34">
         <v>432332.63577457902</v>
       </c>
-      <c r="X33">
+      <c r="X34">
         <v>76633.207778455893</v>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <v>153266.415556911</v>
       </c>
-      <c r="Z33">
+      <c r="Z34">
         <v>-4579.8958977517204</v>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <v>-1789751.44544721</v>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <v>599.73654430174201</v>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <v>98.133723673196201</v>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <v>1.54252978251027</v>
       </c>
-      <c r="AE33">
+      <c r="AE34">
         <v>1.54252978251027</v>
       </c>
-      <c r="AF33">
+      <c r="AF34">
         <v>1.3175347732039699</v>
       </c>
-      <c r="AG33">
+      <c r="AG34">
         <v>1.3365776909337499</v>
       </c>
-      <c r="AH33">
+      <c r="AH34">
         <v>1.4734022213829701</v>
       </c>
-      <c r="AI33" t="s">
+      <c r="AI34" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="22" t="str">
-        <f>T34</f>
+      <c r="B35" s="20" t="str">
+        <f>T35</f>
         <v>[85,90)</v>
       </c>
-      <c r="C34" s="23">
-        <f>V34/1000</f>
+      <c r="C35" s="21">
+        <f>V35/1000</f>
         <v>940.56899999999996</v>
       </c>
-      <c r="D34" s="17">
+      <c r="D35" s="15">
         <f t="shared" si="64"/>
         <v>344.866124798366</v>
       </c>
-      <c r="E34" s="18">
+      <c r="E35" s="25">
         <f t="shared" si="53"/>
         <v>46.888656095831699</v>
       </c>
-      <c r="F34" s="19">
+      <c r="F35" s="26">
         <f t="shared" si="54"/>
         <v>1.6188368812010501</v>
       </c>
-      <c r="G34" s="17">
+      <c r="G35" s="15">
         <f t="shared" si="55"/>
         <v>93.777312191663498</v>
       </c>
-      <c r="H34" s="19">
+      <c r="H35" s="26">
         <f t="shared" si="56"/>
         <v>1.6188368812010501</v>
       </c>
-      <c r="I34" s="17">
+      <c r="I35" s="15">
         <f t="shared" si="57"/>
         <v>2446.1601279562801</v>
       </c>
-      <c r="J34" s="19">
+      <c r="J35" s="26">
         <f t="shared" si="58"/>
         <v>1.3572176804580001</v>
       </c>
-      <c r="K34" s="17">
+      <c r="K35" s="15">
         <f t="shared" si="59"/>
         <v>210.052717532841</v>
       </c>
-      <c r="L34" s="19">
+      <c r="L35" s="26">
         <f t="shared" si="60"/>
         <v>1.3702713671573701</v>
       </c>
-      <c r="M34" s="20">
+      <c r="M35" s="27">
         <f t="shared" si="61"/>
         <v>0.72697001475812495</v>
       </c>
-      <c r="N34" s="19">
+      <c r="N35" s="26">
         <f t="shared" si="62"/>
         <v>1.52866814545388</v>
       </c>
-      <c r="O34" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$32:K34)) * 20 + (SUM($M$3:$M$5) + SUM($M$32:M34)) * 1000) /(SUM($G$3:$G$5) + SUM($G$32:G34))</f>
+      <c r="O35" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$33:K35)) * 20 + (SUM($M$4:$M$6) + SUM($M$33:M35)) * 1000) /(SUM($G$4:$G$6) + SUM($G$33:G35))</f>
         <v>95.985057498780066</v>
       </c>
-      <c r="P34" s="20">
+      <c r="P35" s="27">
         <f t="shared" si="65"/>
         <v>52.550283754592733</v>
       </c>
-      <c r="Q34" s="18">
+      <c r="Q35" s="25">
         <f t="shared" si="63"/>
         <v>19.168269305005097</v>
       </c>
-      <c r="S34" t="s">
+      <c r="S35" t="s">
         <v>53</v>
-      </c>
-      <c r="T34" t="s">
-        <v>4</v>
-      </c>
-      <c r="U34" t="s">
-        <v>58</v>
-      </c>
-      <c r="V34">
-        <v>940569</v>
-      </c>
-      <c r="W34">
-        <v>344866.12479836599</v>
-      </c>
-      <c r="X34">
-        <v>46888.656095831699</v>
-      </c>
-      <c r="Y34">
-        <v>93777.312191663499</v>
-      </c>
-      <c r="Z34">
-        <v>-2446.1601279562801</v>
-      </c>
-      <c r="AA34">
-        <v>-726970.01475812495</v>
-      </c>
-      <c r="AB34">
-        <v>210.052717532841</v>
-      </c>
-      <c r="AC34">
-        <v>95.985057498779994</v>
-      </c>
-      <c r="AD34">
-        <v>1.6188368812010501</v>
-      </c>
-      <c r="AE34">
-        <v>1.6188368812010501</v>
-      </c>
-      <c r="AF34">
-        <v>1.3572176804580001</v>
-      </c>
-      <c r="AG34">
-        <v>1.3702713671573701</v>
-      </c>
-      <c r="AH34">
-        <v>1.52866814545388</v>
-      </c>
-      <c r="AI34" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B35" s="22"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="17">
-        <f t="shared" si="64"/>
-        <v>595.70287520163299</v>
-      </c>
-      <c r="E35" s="18">
-        <f t="shared" si="53"/>
-        <v>80.992899105293191</v>
-      </c>
-      <c r="F35" s="19">
-        <f t="shared" si="54"/>
-        <v>1.7506455884638199</v>
-      </c>
-      <c r="G35" s="17">
-        <f t="shared" si="55"/>
-        <v>161.98579821058601</v>
-      </c>
-      <c r="H35" s="19">
-        <f t="shared" si="56"/>
-        <v>1.7506455884638199</v>
-      </c>
-      <c r="I35" s="17">
-        <f t="shared" si="57"/>
-        <v>3421.9017297001901</v>
-      </c>
-      <c r="J35" s="19">
-        <f t="shared" si="58"/>
-        <v>1.41272958559462</v>
-      </c>
-      <c r="K35" s="17">
-        <f t="shared" si="59"/>
-        <v>489.89476123665298</v>
-      </c>
-      <c r="L35" s="19">
-        <f t="shared" si="60"/>
-        <v>1.44885333297353</v>
-      </c>
-      <c r="M35" s="20">
-        <f t="shared" si="61"/>
-        <v>1.71789924427458</v>
-      </c>
-      <c r="N35" s="19">
-        <f t="shared" si="62"/>
-        <v>1.65926677712804</v>
-      </c>
-      <c r="O35" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$32:K35)) * 20 + (SUM($M$3:$M$5) + SUM($M$32:M35)) * 1000) /(SUM($G$3:$G$5) + SUM($G$32:G35))</f>
-        <v>94.110775783860802</v>
-      </c>
-      <c r="P35" s="20">
-        <f t="shared" si="65"/>
-        <v>71.091383295446619</v>
-      </c>
-      <c r="Q35" s="18">
-        <f t="shared" si="63"/>
-        <v>23.668972841131058</v>
-      </c>
-      <c r="S35" t="s">
-        <v>54</v>
       </c>
       <c r="T35" t="s">
         <v>4</v>
       </c>
       <c r="U35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V35">
         <v>940569</v>
       </c>
       <c r="W35">
-        <v>595702.87520163297</v>
+        <v>344866.12479836599</v>
       </c>
       <c r="X35">
-        <v>80992.899105293196</v>
+        <v>46888.656095831699</v>
       </c>
       <c r="Y35">
-        <v>161985.79821058601</v>
+        <v>93777.312191663499</v>
       </c>
       <c r="Z35">
-        <v>-3421.9017297001901</v>
+        <v>-2446.1601279562801</v>
       </c>
       <c r="AA35">
-        <v>-1717899.2442745799</v>
+        <v>-726970.01475812495</v>
       </c>
       <c r="AB35">
-        <v>489.89476123665298</v>
+        <v>210.052717532841</v>
       </c>
       <c r="AC35">
-        <v>94.110775783860703</v>
+        <v>95.985057498779994</v>
       </c>
       <c r="AD35">
-        <v>1.7506455884638199</v>
+        <v>1.6188368812010501</v>
       </c>
       <c r="AE35">
-        <v>1.7506455884638199</v>
+        <v>1.6188368812010501</v>
       </c>
       <c r="AF35">
-        <v>1.41272958559462</v>
+        <v>1.3572176804580001</v>
       </c>
       <c r="AG35">
-        <v>1.44885333297353</v>
+        <v>1.3702713671573701</v>
       </c>
       <c r="AH35">
-        <v>1.65926677712804</v>
+        <v>1.52866814545388</v>
       </c>
       <c r="AI35" t="s">
         <v>64</v>
@@ -3960,117 +3948,111 @@
       <c r="A36" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B36" s="15" t="str">
-        <f>T36</f>
-        <v>[90,95)</v>
-      </c>
-      <c r="C36" s="16">
-        <f>V36/1000</f>
-        <v>417.13799999999998</v>
-      </c>
-      <c r="D36" s="17">
+      <c r="B36" s="20"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="15">
         <f t="shared" si="64"/>
-        <v>417.13799999999998</v>
-      </c>
-      <c r="E36" s="18">
+        <v>595.70287520163299</v>
+      </c>
+      <c r="E36" s="25">
         <f t="shared" si="53"/>
-        <v>56.714878093459198</v>
-      </c>
-      <c r="F36" s="19">
+        <v>80.992899105293191</v>
+      </c>
+      <c r="F36" s="26">
         <f t="shared" si="54"/>
-        <v>1.8429439855658301</v>
-      </c>
-      <c r="G36" s="17">
+        <v>1.7506455884638199</v>
+      </c>
+      <c r="G36" s="15">
         <f t="shared" si="55"/>
-        <v>113.42975618691801</v>
-      </c>
-      <c r="H36" s="19">
+        <v>161.98579821058601</v>
+      </c>
+      <c r="H36" s="26">
         <f t="shared" si="56"/>
-        <v>1.8429439855658301</v>
-      </c>
-      <c r="I36" s="17">
+        <v>1.7506455884638199</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="57"/>
-        <v>1687.40184965618</v>
-      </c>
-      <c r="J36" s="19">
+        <v>3421.9017297001901</v>
+      </c>
+      <c r="J36" s="26">
         <f t="shared" si="58"/>
-        <v>1.4401035135459801</v>
-      </c>
-      <c r="K36" s="17">
+        <v>1.41272958559462</v>
+      </c>
+      <c r="K36" s="15">
         <f t="shared" si="59"/>
-        <v>254.776716327858</v>
-      </c>
-      <c r="L36" s="19">
+        <v>489.89476123665298</v>
+      </c>
+      <c r="L36" s="26">
         <f t="shared" si="60"/>
-        <v>1.48972099843435</v>
-      </c>
-      <c r="M36" s="20">
+        <v>1.44885333297353</v>
+      </c>
+      <c r="M36" s="27">
         <f t="shared" si="61"/>
-        <v>1.0028080909625301</v>
-      </c>
-      <c r="N36" s="19">
+        <v>1.71789924427458</v>
+      </c>
+      <c r="N36" s="26">
         <f t="shared" si="62"/>
-        <v>1.7355025429612001</v>
-      </c>
-      <c r="O36" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$32:K36)) * 20 + (SUM($M$3:$M$5) + SUM($M$32:M36)) * 1000) /(SUM($G$3:$G$5) + SUM($G$32:G36))</f>
-        <v>92.090084943841546</v>
-      </c>
-      <c r="P36" s="20">
+        <v>1.65926677712804</v>
+      </c>
+      <c r="O36" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$33:K36)) * 20 + (SUM($M$4:$M$6) + SUM($M$33:M36)) * 1000) /(SUM($G$4:$G$6) + SUM($G$33:G36))</f>
+        <v>94.110775783860802</v>
+      </c>
+      <c r="P36" s="27">
         <f t="shared" si="65"/>
-        <v>53.763162529154933</v>
-      </c>
-      <c r="Q36" s="18">
+        <v>71.091383295446619</v>
+      </c>
+      <c r="Q36" s="25">
         <f t="shared" si="63"/>
-        <v>33.610771556885069</v>
+        <v>23.668972841131058</v>
       </c>
       <c r="S36" t="s">
         <v>54</v>
       </c>
       <c r="T36" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U36" t="s">
         <v>59</v>
       </c>
       <c r="V36">
-        <v>417138</v>
+        <v>940569</v>
       </c>
       <c r="W36">
-        <v>417138</v>
+        <v>595702.87520163297</v>
       </c>
       <c r="X36">
-        <v>56714.8780934592</v>
+        <v>80992.899105293196</v>
       </c>
       <c r="Y36">
-        <v>113429.75618691801</v>
+        <v>161985.79821058601</v>
       </c>
       <c r="Z36">
-        <v>-1687.40184965618</v>
+        <v>-3421.9017297001901</v>
       </c>
       <c r="AA36">
-        <v>-1002808.09096253</v>
+        <v>-1717899.2442745799</v>
       </c>
       <c r="AB36">
-        <v>254.776716327858</v>
+        <v>489.89476123665298</v>
       </c>
       <c r="AC36">
-        <v>92.090084943841504</v>
+        <v>94.110775783860703</v>
       </c>
       <c r="AD36">
-        <v>1.8429439855658301</v>
+        <v>1.7506455884638199</v>
       </c>
       <c r="AE36">
-        <v>1.8429439855658301</v>
+        <v>1.7506455884638199</v>
       </c>
       <c r="AF36">
-        <v>1.4401035135459801</v>
+        <v>1.41272958559462</v>
       </c>
       <c r="AG36">
-        <v>1.48972099843435</v>
+        <v>1.44885333297353</v>
       </c>
       <c r="AH36">
-        <v>1.7355025429612001</v>
+        <v>1.65926677712804</v>
       </c>
       <c r="AI36" t="s">
         <v>64</v>
@@ -4080,150 +4062,271 @@
       <c r="A37" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B37" s="15" t="str">
+      <c r="B37" s="14" t="str">
         <f>T37</f>
+        <v>[90,95)</v>
+      </c>
+      <c r="C37" s="15">
+        <f>V37/1000</f>
+        <v>417.13799999999998</v>
+      </c>
+      <c r="D37" s="15">
+        <f t="shared" si="64"/>
+        <v>417.13799999999998</v>
+      </c>
+      <c r="E37" s="25">
+        <f t="shared" si="53"/>
+        <v>56.714878093459198</v>
+      </c>
+      <c r="F37" s="26">
+        <f t="shared" si="54"/>
+        <v>1.8429439855658301</v>
+      </c>
+      <c r="G37" s="15">
+        <f t="shared" si="55"/>
+        <v>113.42975618691801</v>
+      </c>
+      <c r="H37" s="26">
+        <f t="shared" si="56"/>
+        <v>1.8429439855658301</v>
+      </c>
+      <c r="I37" s="15">
+        <f t="shared" si="57"/>
+        <v>1687.40184965618</v>
+      </c>
+      <c r="J37" s="26">
+        <f t="shared" si="58"/>
+        <v>1.4401035135459801</v>
+      </c>
+      <c r="K37" s="15">
+        <f t="shared" si="59"/>
+        <v>254.776716327858</v>
+      </c>
+      <c r="L37" s="26">
+        <f t="shared" si="60"/>
+        <v>1.48972099843435</v>
+      </c>
+      <c r="M37" s="27">
+        <f t="shared" si="61"/>
+        <v>1.0028080909625301</v>
+      </c>
+      <c r="N37" s="26">
+        <f t="shared" si="62"/>
+        <v>1.7355025429612001</v>
+      </c>
+      <c r="O37" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$33:K37)) * 20 + (SUM($M$4:$M$6) + SUM($M$33:M37)) * 1000) /(SUM($G$4:$G$6) + SUM($G$33:G37))</f>
+        <v>92.090084943841546</v>
+      </c>
+      <c r="P37" s="27">
+        <f t="shared" si="65"/>
+        <v>53.763162529154933</v>
+      </c>
+      <c r="Q37" s="25">
+        <f t="shared" si="63"/>
+        <v>33.610771556885069</v>
+      </c>
+      <c r="S37" t="s">
+        <v>54</v>
+      </c>
+      <c r="T37" t="s">
+        <v>5</v>
+      </c>
+      <c r="U37" t="s">
+        <v>59</v>
+      </c>
+      <c r="V37">
+        <v>417138</v>
+      </c>
+      <c r="W37">
+        <v>417138</v>
+      </c>
+      <c r="X37">
+        <v>56714.8780934592</v>
+      </c>
+      <c r="Y37">
+        <v>113429.75618691801</v>
+      </c>
+      <c r="Z37">
+        <v>-1687.40184965618</v>
+      </c>
+      <c r="AA37">
+        <v>-1002808.09096253</v>
+      </c>
+      <c r="AB37">
+        <v>254.776716327858</v>
+      </c>
+      <c r="AC37">
+        <v>92.090084943841504</v>
+      </c>
+      <c r="AD37">
+        <v>1.8429439855658301</v>
+      </c>
+      <c r="AE37">
+        <v>1.8429439855658301</v>
+      </c>
+      <c r="AF37">
+        <v>1.4401035135459801</v>
+      </c>
+      <c r="AG37">
+        <v>1.48972099843435</v>
+      </c>
+      <c r="AH37">
+        <v>1.7355025429612001</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="14" t="str">
+        <f>T38</f>
         <v>[95,100)</v>
       </c>
-      <c r="C37" s="16">
-        <f>V37/1000</f>
+      <c r="C38" s="15">
+        <f>V38/1000</f>
         <v>109.06399999999999</v>
       </c>
-      <c r="D37" s="17">
+      <c r="D38" s="15">
         <f t="shared" si="64"/>
         <v>109.06399999999999</v>
       </c>
-      <c r="E37" s="18">
+      <c r="E38" s="25">
         <f t="shared" si="53"/>
         <v>14.8285494593756</v>
       </c>
-      <c r="F37" s="19">
+      <c r="F38" s="26">
         <f t="shared" si="54"/>
         <v>1.86707612500538</v>
       </c>
-      <c r="G37" s="17">
+      <c r="G38" s="15">
         <f t="shared" si="55"/>
         <v>29.657098918751302</v>
       </c>
-      <c r="H37" s="19">
+      <c r="H38" s="26">
         <f t="shared" si="56"/>
         <v>1.86707612500538</v>
       </c>
-      <c r="I37" s="17">
+      <c r="I38" s="15">
         <f t="shared" si="57"/>
         <v>277.23480019250798</v>
       </c>
-      <c r="J37" s="19">
+      <c r="J38" s="26">
         <f t="shared" si="58"/>
         <v>1.4446009635444099</v>
       </c>
-      <c r="K37" s="17">
+      <c r="K38" s="15">
         <f t="shared" si="59"/>
         <v>40.5672077956918</v>
       </c>
-      <c r="L37" s="19">
+      <c r="L38" s="26">
         <f t="shared" si="60"/>
         <v>1.4962282142457899</v>
       </c>
-      <c r="M37" s="20">
+      <c r="M38" s="27">
         <f t="shared" si="61"/>
         <v>0.16826237552079701</v>
       </c>
-      <c r="N37" s="19">
+      <c r="N38" s="26">
         <f t="shared" si="62"/>
         <v>1.7482942337885301</v>
       </c>
-      <c r="O37" s="20">
-        <f>((SUM($K$3:$K$5)+ SUM($K$32:K37)) * 20 + (SUM($M$3:$M$5) + SUM($M$32:M37)) * 1000) /(SUM($G$3:$G$5) + SUM($G$32:G37))</f>
+      <c r="O38" s="27">
+        <f>((SUM($K$4:$K$6)+ SUM($K$33:K38)) * 20 + (SUM($M$4:$M$6) + SUM($M$33:M38)) * 1000) /(SUM($G$4:$G$6) + SUM($G$33:G38))</f>
         <v>91.326741823223799</v>
       </c>
-      <c r="P37" s="20">
+      <c r="P38" s="27">
         <f t="shared" si="65"/>
         <v>33.03109768485335</v>
       </c>
-      <c r="Q37" s="18">
+      <c r="Q38" s="25">
         <f t="shared" si="63"/>
         <v>53.487330771890328</v>
       </c>
-      <c r="S37" t="s">
+      <c r="S38" t="s">
         <v>55</v>
       </c>
-      <c r="T37" t="s">
+      <c r="T38" t="s">
         <v>28</v>
       </c>
-      <c r="U37" t="s">
+      <c r="U38" t="s">
         <v>59</v>
       </c>
-      <c r="V37">
+      <c r="V38">
         <v>109064</v>
       </c>
-      <c r="W37">
+      <c r="W38">
         <v>109064</v>
       </c>
-      <c r="X37">
+      <c r="X38">
         <v>14828.549459375599</v>
       </c>
-      <c r="Y37">
+      <c r="Y38">
         <v>29657.098918751301</v>
       </c>
-      <c r="Z37">
+      <c r="Z38">
         <v>-277.23480019250798</v>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <v>-168262.37552079701</v>
       </c>
-      <c r="AB37">
+      <c r="AB38">
         <v>40.5672077956918</v>
       </c>
-      <c r="AC37">
+      <c r="AC38">
         <v>91.326741823223699</v>
       </c>
-      <c r="AD37">
+      <c r="AD38">
         <v>1.86707612500538</v>
       </c>
-      <c r="AE37">
+      <c r="AE38">
         <v>1.86707612500538</v>
       </c>
-      <c r="AF37">
+      <c r="AF38">
         <v>1.4446009635444099</v>
       </c>
-      <c r="AG37">
+      <c r="AG38">
         <v>1.4962282142457899</v>
       </c>
-      <c r="AH37">
+      <c r="AH38">
         <v>1.7482942337885301</v>
       </c>
-      <c r="AI37" t="s">
+      <c r="AI38" t="s">
         <v>64</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="A15:O15"/>
+  <mergeCells count="27">
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="A32:O32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A7:O7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="A23:O23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="A31:O31"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A8:Q8"/>
+    <mergeCell ref="A16:Q16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
